--- a/亿纬锂能DA梳理.xlsx
+++ b/亿纬锂能DA梳理.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="542">
   <si>
     <t>业务对象</t>
   </si>
@@ -892,6 +892,153 @@
     <t>20GP/40HQ</t>
   </si>
   <si>
+    <t>clm_calc_bom_head</t>
+  </si>
+  <si>
+    <t>实例BOM头信息</t>
+  </si>
+  <si>
+    <t>bom_header_id</t>
+  </si>
+  <si>
+    <t>bom清单头ID</t>
+  </si>
+  <si>
+    <t>bom_name</t>
+  </si>
+  <si>
+    <t>物料清单名称</t>
+  </si>
+  <si>
+    <t>product_item_id</t>
+  </si>
+  <si>
+    <t>产品编码ID</t>
+  </si>
+  <si>
+    <t>product_item_code</t>
+  </si>
+  <si>
+    <t>产品编码</t>
+  </si>
+  <si>
+    <t>product_item_name</t>
+  </si>
+  <si>
+    <t>产品名称</t>
+  </si>
+  <si>
+    <t>product_item_spec</t>
+  </si>
+  <si>
+    <t>规格型号</t>
+  </si>
+  <si>
+    <t>basis_quantity</t>
+  </si>
+  <si>
+    <t>基准数量</t>
+  </si>
+  <si>
+    <t>bom_version</t>
+  </si>
+  <si>
+    <t>BOM版本</t>
+  </si>
+  <si>
+    <t>clm_calc_bom_line</t>
+  </si>
+  <si>
+    <t>实例BOM行信息</t>
+  </si>
+  <si>
+    <t>ref_bom_header_id</t>
+  </si>
+  <si>
+    <t>bom_line_id</t>
+  </si>
+  <si>
+    <t>物料清单行ID</t>
+  </si>
+  <si>
+    <t>seq_num</t>
+  </si>
+  <si>
+    <t>序号</t>
+  </si>
+  <si>
+    <t>component_item_id</t>
+  </si>
+  <si>
+    <t>组件ID</t>
+  </si>
+  <si>
+    <t>component_item_code</t>
+  </si>
+  <si>
+    <t>组件编码</t>
+  </si>
+  <si>
+    <t>component_item_name</t>
+  </si>
+  <si>
+    <t>组件名称</t>
+  </si>
+  <si>
+    <t>component_item_spec</t>
+  </si>
+  <si>
+    <t>组件规格型号</t>
+  </si>
+  <si>
+    <t>component_item_quantity</t>
+  </si>
+  <si>
+    <t>物料清单组件数量</t>
+  </si>
+  <si>
+    <t>component_item_uom_code</t>
+  </si>
+  <si>
+    <t>物料用量单位编码</t>
+  </si>
+  <si>
+    <t>parent_line_id</t>
+  </si>
+  <si>
+    <t>父级行ID（多级树，顶层为空）</t>
+  </si>
+  <si>
+    <t>material_unit_price</t>
+  </si>
+  <si>
+    <t>材料单价</t>
+  </si>
+  <si>
+    <t>direct_labor_unit_price</t>
+  </si>
+  <si>
+    <t>直接人工单价</t>
+  </si>
+  <si>
+    <t>indirect_labor_unit_price</t>
+  </si>
+  <si>
+    <t>间接人工单价</t>
+  </si>
+  <si>
+    <t>machine_cost</t>
+  </si>
+  <si>
+    <t>机器费用</t>
+  </si>
+  <si>
+    <t>other_charge</t>
+  </si>
+  <si>
+    <t>其他制费</t>
+  </si>
+  <si>
     <t>clm_calc_markup_item</t>
   </si>
   <si>
@@ -910,132 +1057,129 @@
     <t>枚举值</t>
   </si>
   <si>
-    <t>seq_num</t>
-  </si>
-  <si>
-    <t>序号</t>
+    <t>定价/报价</t>
+  </si>
+  <si>
+    <t>markup_item_name</t>
+  </si>
+  <si>
+    <t>加价项名称</t>
+  </si>
+  <si>
+    <t>markup_value</t>
+  </si>
+  <si>
+    <t>加价值</t>
+  </si>
+  <si>
+    <t>报价单</t>
+  </si>
+  <si>
+    <t>clm_quote_base_info</t>
+  </si>
+  <si>
+    <t>报价基本信息</t>
+  </si>
+  <si>
+    <t>quote_order_id</t>
+  </si>
+  <si>
+    <t>报价单id</t>
+  </si>
+  <si>
+    <t>quote_order_no</t>
+  </si>
+  <si>
+    <t>报价单号</t>
+  </si>
+  <si>
+    <t>quote_order_name</t>
+  </si>
+  <si>
+    <t>报价单名称</t>
+  </si>
+  <si>
+    <t>关联测算单号</t>
+  </si>
+  <si>
+    <t>quote_form</t>
+  </si>
+  <si>
+    <t>报价形式</t>
+  </si>
+  <si>
+    <t>quote_type</t>
+  </si>
+  <si>
+    <t>报价类型</t>
+  </si>
+  <si>
+    <t>quote_template</t>
+  </si>
+  <si>
+    <t>报价模板</t>
+  </si>
+  <si>
+    <t>quote_valid_days</t>
+  </si>
+  <si>
+    <t>报价有效天数</t>
+  </si>
+  <si>
+    <t>文本/枚举</t>
+  </si>
+  <si>
+    <t>is_sealed</t>
+  </si>
+  <si>
+    <t>是否用印</t>
+  </si>
+  <si>
+    <t>sign_entity</t>
+  </si>
+  <si>
+    <t>签约主体</t>
+  </si>
+  <si>
+    <t>sign_entity_address</t>
+  </si>
+  <si>
+    <t>签约主体地址</t>
+  </si>
+  <si>
+    <t>sign_entity_credit_code</t>
+  </si>
+  <si>
+    <t>签约主体社会信用代码</t>
+  </si>
+  <si>
+    <t>quote_contact</t>
+  </si>
+  <si>
+    <t>报价联系人</t>
+  </si>
+  <si>
+    <t>quote_contact_phone</t>
+  </si>
+  <si>
+    <t>报价联系人电话</t>
+  </si>
+  <si>
+    <t>quote_contact_dept</t>
+  </si>
+  <si>
+    <t>报价联系人部门</t>
+  </si>
+  <si>
+    <t>apply_date</t>
+  </si>
+  <si>
+    <t>申请日期</t>
   </si>
   <si>
     <t>日期</t>
   </si>
   <si>
-    <t>markup_item_name</t>
-  </si>
-  <si>
-    <t>加价项名称</t>
-  </si>
-  <si>
-    <t>markup_value</t>
-  </si>
-  <si>
-    <t>加价值</t>
-  </si>
-  <si>
-    <t>报价单</t>
-  </si>
-  <si>
-    <t>clm_quote_base_info</t>
-  </si>
-  <si>
-    <t>报价基本信息</t>
-  </si>
-  <si>
-    <t>quote_order_id</t>
-  </si>
-  <si>
-    <t>报价单id</t>
-  </si>
-  <si>
-    <t>quote_order_no</t>
-  </si>
-  <si>
-    <t>报价单号</t>
-  </si>
-  <si>
-    <t>quote_order_name</t>
-  </si>
-  <si>
-    <t>报价单名称</t>
-  </si>
-  <si>
-    <t>关联测算单号</t>
-  </si>
-  <si>
-    <t>quote_form</t>
-  </si>
-  <si>
-    <t>报价形式</t>
-  </si>
-  <si>
-    <t>quote_type</t>
-  </si>
-  <si>
-    <t>报价类型</t>
-  </si>
-  <si>
-    <t>quote_template</t>
-  </si>
-  <si>
-    <t>报价模板</t>
-  </si>
-  <si>
-    <t>quote_valid_days</t>
-  </si>
-  <si>
-    <t>报价有效天数</t>
-  </si>
-  <si>
-    <t>文本/枚举</t>
-  </si>
-  <si>
-    <t>is_sealed</t>
-  </si>
-  <si>
-    <t>是否用印</t>
-  </si>
-  <si>
-    <t>sign_entity</t>
-  </si>
-  <si>
-    <t>签约主体</t>
-  </si>
-  <si>
-    <t>sign_entity_address</t>
-  </si>
-  <si>
-    <t>签约主体地址</t>
-  </si>
-  <si>
-    <t>sign_entity_credit_code</t>
-  </si>
-  <si>
-    <t>签约主体社会信用代码</t>
-  </si>
-  <si>
-    <t>quote_contact</t>
-  </si>
-  <si>
-    <t>报价联系人</t>
-  </si>
-  <si>
-    <t>quote_contact_phone</t>
-  </si>
-  <si>
-    <t>报价联系人电话</t>
-  </si>
-  <si>
-    <t>quote_contact_dept</t>
-  </si>
-  <si>
-    <t>报价联系人部门</t>
-  </si>
-  <si>
-    <t>apply_date</t>
-  </si>
-  <si>
-    <t>申请日期</t>
-  </si>
-  <si>
     <t>customer_address</t>
   </si>
   <si>
@@ -1097,147 +1241,6 @@
   </si>
   <si>
     <t>税金</t>
-  </si>
-  <si>
-    <t>clm_calc_bom_head</t>
-  </si>
-  <si>
-    <t>实例BOM头信息</t>
-  </si>
-  <si>
-    <t>bom_header_id</t>
-  </si>
-  <si>
-    <t>bom清单头ID</t>
-  </si>
-  <si>
-    <t>bom_name</t>
-  </si>
-  <si>
-    <t>物料清单名称</t>
-  </si>
-  <si>
-    <t>product_item_id</t>
-  </si>
-  <si>
-    <t>产品编码ID</t>
-  </si>
-  <si>
-    <t>product_item_code</t>
-  </si>
-  <si>
-    <t>产品编码</t>
-  </si>
-  <si>
-    <t>product_item_name</t>
-  </si>
-  <si>
-    <t>产品名称</t>
-  </si>
-  <si>
-    <t>product_item_spec</t>
-  </si>
-  <si>
-    <t>规格型号</t>
-  </si>
-  <si>
-    <t>basis_quantity</t>
-  </si>
-  <si>
-    <t>基准数量</t>
-  </si>
-  <si>
-    <t>bom_version</t>
-  </si>
-  <si>
-    <t>BOM版本</t>
-  </si>
-  <si>
-    <t>clm_calc_bom_line</t>
-  </si>
-  <si>
-    <t>实例BOM行信息</t>
-  </si>
-  <si>
-    <t>ref_bom_header_id</t>
-  </si>
-  <si>
-    <t>bom_line_id</t>
-  </si>
-  <si>
-    <t>物料清单行ID</t>
-  </si>
-  <si>
-    <t>component_item_id</t>
-  </si>
-  <si>
-    <t>组件ID</t>
-  </si>
-  <si>
-    <t>component_item_code</t>
-  </si>
-  <si>
-    <t>组件编码</t>
-  </si>
-  <si>
-    <t>component_item_name</t>
-  </si>
-  <si>
-    <t>组件名称</t>
-  </si>
-  <si>
-    <t>component_item_spec</t>
-  </si>
-  <si>
-    <t>组件规格型号</t>
-  </si>
-  <si>
-    <t>component_item_quantity</t>
-  </si>
-  <si>
-    <t>物料清单组件数量</t>
-  </si>
-  <si>
-    <t>component_item_uom_code</t>
-  </si>
-  <si>
-    <t>物料用量单位编码</t>
-  </si>
-  <si>
-    <t>parent_line_id</t>
-  </si>
-  <si>
-    <t>父级行ID（多级树，顶层为空）</t>
-  </si>
-  <si>
-    <t>material_unit_price</t>
-  </si>
-  <si>
-    <t>材料单价</t>
-  </si>
-  <si>
-    <t>direct_labor_unit_price</t>
-  </si>
-  <si>
-    <t>直接人工单价</t>
-  </si>
-  <si>
-    <t>indirect_labor_unit_price</t>
-  </si>
-  <si>
-    <t>间接人工单价</t>
-  </si>
-  <si>
-    <t>machine_cost</t>
-  </si>
-  <si>
-    <t>机器费用</t>
-  </si>
-  <si>
-    <t>other_charge</t>
-  </si>
-  <si>
-    <t>其他制费</t>
   </si>
   <si>
     <t>逻辑实体</t>
@@ -2364,7 +2367,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2430,6 +2433,25 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2447,18 +2469,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5912,16 +5922,16 @@
       </c>
     </row>
     <row r="123" spans="1:9">
-      <c r="A123" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B123" s="8" t="s">
+      <c r="A123" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B123" s="25" t="s">
         <v>279</v>
       </c>
-      <c r="C123" s="8" t="s">
+      <c r="C123" s="25" t="s">
         <v>280</v>
       </c>
-      <c r="D123" s="8" t="s">
+      <c r="D123" s="25" t="s">
         <v>12</v>
       </c>
       <c r="E123" s="9" t="s">
@@ -5937,17 +5947,17 @@
       <c r="I123" s="12"/>
     </row>
     <row r="124" spans="1:9">
-      <c r="A124" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B124" s="8" t="s">
+      <c r="A124" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B124" s="25" t="s">
         <v>279</v>
       </c>
-      <c r="C124" s="8" t="s">
+      <c r="C124" s="25" t="s">
         <v>280</v>
       </c>
-      <c r="D124" s="8" t="s">
-        <v>281</v>
+      <c r="D124" s="25" t="s">
+        <v>155</v>
       </c>
       <c r="E124" s="9" t="s">
         <v>156</v>
@@ -5955,600 +5965,608 @@
       <c r="F124" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G124" s="11" t="s">
-        <v>15</v>
-      </c>
+      <c r="G124" s="11"/>
       <c r="H124" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I124" s="12"/>
     </row>
     <row r="125" spans="1:9">
-      <c r="A125" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B125" s="8" t="s">
+      <c r="A125" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B125" s="25" t="s">
         <v>279</v>
       </c>
-      <c r="C125" s="8" t="s">
+      <c r="C125" s="25" t="s">
         <v>280</v>
       </c>
-      <c r="D125" s="8" t="s">
+      <c r="D125" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="E125" s="25" t="s">
         <v>282</v>
       </c>
-      <c r="E125" s="9" t="s">
+      <c r="F125" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G125" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="H125" s="22"/>
+      <c r="I125" s="12"/>
+    </row>
+    <row r="126" spans="1:9">
+      <c r="A126" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B126" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="C126" s="25" t="s">
+        <v>280</v>
+      </c>
+      <c r="D126" s="25" t="s">
         <v>283</v>
       </c>
-      <c r="F125" s="10" t="s">
+      <c r="E126" s="25" t="s">
         <v>284</v>
       </c>
-      <c r="G125" s="11"/>
-      <c r="H125" s="11"/>
-      <c r="I125" s="12"/>
-    </row>
-    <row r="126" spans="1:9">
-      <c r="A126" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B126" s="8" t="s">
+      <c r="F126" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G126" s="25"/>
+      <c r="H126" s="22"/>
+      <c r="I126" s="12"/>
+    </row>
+    <row r="127" spans="1:9">
+      <c r="A127" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B127" s="25" t="s">
         <v>279</v>
       </c>
-      <c r="C126" s="8" t="s">
+      <c r="C127" s="25" t="s">
         <v>280</v>
       </c>
-      <c r="D126" s="8" t="s">
+      <c r="D127" s="25" t="s">
         <v>285</v>
       </c>
-      <c r="E126" s="9" t="s">
+      <c r="E127" s="25" t="s">
         <v>286</v>
       </c>
-      <c r="F126" s="10" t="s">
+      <c r="F127" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G127" s="25"/>
+      <c r="H127" s="22"/>
+      <c r="I127" s="12"/>
+    </row>
+    <row r="128" spans="1:9">
+      <c r="A128" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B128" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="C128" s="25" t="s">
+        <v>280</v>
+      </c>
+      <c r="D128" s="25" t="s">
         <v>287</v>
       </c>
-      <c r="G126" s="11"/>
-      <c r="H126" s="11"/>
-      <c r="I126" s="12"/>
-    </row>
-    <row r="127" spans="1:9">
-      <c r="A127" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B127" s="8" t="s">
+      <c r="E128" s="25" t="s">
+        <v>288</v>
+      </c>
+      <c r="F128" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G128" s="25"/>
+      <c r="H128" s="22"/>
+      <c r="I128" s="12"/>
+    </row>
+    <row r="129" spans="1:9">
+      <c r="A129" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B129" s="25" t="s">
         <v>279</v>
       </c>
-      <c r="C127" s="8" t="s">
+      <c r="C129" s="25" t="s">
         <v>280</v>
       </c>
-      <c r="D127" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="E127" s="9" t="s">
+      <c r="D129" s="25" t="s">
         <v>289</v>
       </c>
-      <c r="F127" s="10" t="s">
+      <c r="E129" s="25" t="s">
+        <v>290</v>
+      </c>
+      <c r="F129" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="G127" s="11"/>
-      <c r="H127" s="11"/>
-      <c r="I127" s="12"/>
-    </row>
-    <row r="128" spans="1:9">
-      <c r="A128" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B128" s="8" t="s">
+      <c r="G129" s="25"/>
+      <c r="H129" s="22"/>
+      <c r="I129" s="12"/>
+    </row>
+    <row r="130" spans="1:9">
+      <c r="A130" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B130" s="25" t="s">
         <v>279</v>
       </c>
-      <c r="C128" s="8" t="s">
+      <c r="C130" s="25" t="s">
         <v>280</v>
       </c>
-      <c r="D128" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="E128" s="9" t="s">
+      <c r="D130" s="25" t="s">
         <v>291</v>
       </c>
-      <c r="F128" s="10" t="s">
+      <c r="E130" s="25" t="s">
+        <v>292</v>
+      </c>
+      <c r="F130" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="G128" s="11"/>
-      <c r="H128" s="11"/>
-      <c r="I128" s="12"/>
-    </row>
-    <row r="129" spans="1:9">
-      <c r="A129" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B129" s="8" t="s">
+      <c r="G130" s="25"/>
+      <c r="H130" s="22"/>
+      <c r="I130" s="12"/>
+    </row>
+    <row r="131" spans="1:9">
+      <c r="A131" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B131" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="C131" s="25" t="s">
+        <v>280</v>
+      </c>
+      <c r="D131" s="25" t="s">
         <v>293</v>
       </c>
-      <c r="C129" s="8" t="s">
+      <c r="E131" s="25" t="s">
         <v>294</v>
       </c>
-      <c r="D129" s="8" t="s">
+      <c r="F131" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="G131" s="25"/>
+      <c r="H131" s="22"/>
+      <c r="I131" s="12"/>
+    </row>
+    <row r="132" spans="1:9">
+      <c r="A132" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B132" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="C132" s="25" t="s">
+        <v>280</v>
+      </c>
+      <c r="D132" s="25" t="s">
         <v>295</v>
       </c>
-      <c r="E129" s="9" t="s">
+      <c r="E132" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="F129" s="10" t="s">
+      <c r="F132" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="G129" s="11" t="s">
+      <c r="G132" s="25"/>
+      <c r="H132" s="22"/>
+      <c r="I132" s="12"/>
+    </row>
+    <row r="133" spans="1:9">
+      <c r="A133" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B133" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="C133" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="D133" s="25" t="s">
+        <v>299</v>
+      </c>
+      <c r="E133" s="25" t="s">
+        <v>282</v>
+      </c>
+      <c r="F133" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G133" s="25"/>
+      <c r="H133" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="H129" s="11"/>
-      <c r="I129" s="12"/>
-    </row>
-    <row r="130" spans="1:9">
-      <c r="A130" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B130" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="C130" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="D130" s="8" t="s">
+      <c r="I133" s="12"/>
+    </row>
+    <row r="134" spans="1:9">
+      <c r="A134" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B134" s="25" t="s">
         <v>297</v>
       </c>
-      <c r="E130" s="9" t="s">
+      <c r="C134" s="25" t="s">
         <v>298</v>
       </c>
-      <c r="F130" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G130" s="11"/>
-      <c r="H130" s="11"/>
-      <c r="I130" s="12"/>
-    </row>
-    <row r="131" spans="1:9">
-      <c r="A131" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B131" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="C131" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="D131" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="E131" s="9" t="s">
+      <c r="D134" s="25" t="s">
         <v>300</v>
       </c>
-      <c r="F131" s="10" t="s">
+      <c r="E134" s="25" t="s">
+        <v>301</v>
+      </c>
+      <c r="F134" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G131" s="11"/>
-      <c r="H131" s="11"/>
-      <c r="I131" s="12"/>
-    </row>
-    <row r="132" spans="1:9">
-      <c r="A132" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B132" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="C132" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="D132" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E132" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="F132" s="10" t="s">
+      <c r="G134" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="H134" s="22"/>
+      <c r="I134" s="12"/>
+    </row>
+    <row r="135" spans="1:9">
+      <c r="A135" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B135" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="C135" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="D135" s="25" t="s">
+        <v>302</v>
+      </c>
+      <c r="E135" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="F135" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="G135" s="25"/>
+      <c r="H135" s="22"/>
+      <c r="I135" s="12"/>
+    </row>
+    <row r="136" spans="1:9">
+      <c r="A136" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B136" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="C136" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="D136" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="E136" s="25" t="s">
+        <v>305</v>
+      </c>
+      <c r="F136" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="G132" s="11"/>
-      <c r="H132" s="11"/>
-      <c r="I132" s="12"/>
-    </row>
-    <row r="133" spans="1:9">
-      <c r="A133" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B133" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="C133" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="D133" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="E133" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="F133" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G133" s="11"/>
-      <c r="H133" s="11"/>
-      <c r="I133" s="12"/>
-    </row>
-    <row r="134" spans="1:9">
-      <c r="A134" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B134" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="C134" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="D134" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="E134" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="F134" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G134" s="11"/>
-      <c r="H134" s="11"/>
-      <c r="I134" s="12"/>
-    </row>
-    <row r="135" spans="1:9">
-      <c r="A135" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B135" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="C135" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="D135" s="8" t="s">
+      <c r="G136" s="25"/>
+      <c r="H136" s="22"/>
+      <c r="I136" s="12"/>
+    </row>
+    <row r="137" spans="1:9">
+      <c r="A137" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B137" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="C137" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="D137" s="25" t="s">
         <v>306</v>
       </c>
-      <c r="E135" s="9" t="s">
+      <c r="E137" s="25" t="s">
         <v>307</v>
       </c>
-      <c r="F135" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G135" s="11"/>
-      <c r="H135" s="11"/>
-      <c r="I135" s="12"/>
-    </row>
-    <row r="136" spans="1:9">
-      <c r="A136" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B136" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="C136" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="D136" s="8" t="s">
+      <c r="F137" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G137" s="25"/>
+      <c r="H137" s="22"/>
+      <c r="I137" s="12"/>
+    </row>
+    <row r="138" spans="1:9">
+      <c r="A138" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B138" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="C138" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="D138" s="25" t="s">
         <v>308</v>
       </c>
-      <c r="E136" s="9" t="s">
+      <c r="E138" s="25" t="s">
         <v>309</v>
       </c>
-      <c r="F136" s="10" t="s">
+      <c r="F138" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G138" s="25"/>
+      <c r="H138" s="22"/>
+      <c r="I138" s="12"/>
+    </row>
+    <row r="139" spans="1:9">
+      <c r="A139" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B139" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="C139" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="D139" s="25" t="s">
         <v>310</v>
       </c>
-      <c r="G136" s="11"/>
-      <c r="H136" s="11"/>
-      <c r="I136" s="12"/>
-    </row>
-    <row r="137" spans="1:9">
-      <c r="A137" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B137" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="C137" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="D137" s="8" t="s">
+      <c r="E139" s="25" t="s">
         <v>311</v>
       </c>
-      <c r="E137" s="9" t="s">
+      <c r="F139" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G139" s="25"/>
+      <c r="H139" s="22"/>
+      <c r="I139" s="12"/>
+    </row>
+    <row r="140" spans="1:9">
+      <c r="A140" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B140" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="C140" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="D140" s="25" t="s">
         <v>312</v>
       </c>
-      <c r="F137" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G137" s="11"/>
-      <c r="H137" s="11"/>
-      <c r="I137" s="12"/>
-    </row>
-    <row r="138" spans="1:9">
-      <c r="A138" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B138" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="C138" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="D138" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E138" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F138" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="G138" s="11"/>
-      <c r="H138" s="11"/>
-      <c r="I138" s="12"/>
-    </row>
-    <row r="139" spans="1:9">
-      <c r="A139" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B139" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="C139" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="D139" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E139" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="F139" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G139" s="11"/>
-      <c r="H139" s="11"/>
-      <c r="I139" s="12"/>
-    </row>
-    <row r="140" spans="1:9">
-      <c r="A140" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B140" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="C140" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="D140" s="8" t="s">
+      <c r="E140" s="25" t="s">
         <v>313</v>
       </c>
-      <c r="E140" s="9" t="s">
+      <c r="F140" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="G140" s="25"/>
+      <c r="H140" s="22"/>
+      <c r="I140" s="12"/>
+    </row>
+    <row r="141" spans="1:9">
+      <c r="A141" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B141" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="C141" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="D141" s="25" t="s">
         <v>314</v>
       </c>
-      <c r="F140" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G140" s="11"/>
-      <c r="H140" s="11"/>
-      <c r="I140" s="12"/>
-    </row>
-    <row r="141" spans="1:9">
-      <c r="A141" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B141" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="C141" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="D141" s="8" t="s">
+      <c r="E141" s="25" t="s">
         <v>315</v>
       </c>
-      <c r="E141" s="9" t="s">
+      <c r="F141" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G141" s="25"/>
+      <c r="H141" s="22"/>
+      <c r="I141" s="12"/>
+    </row>
+    <row r="142" spans="1:9">
+      <c r="A142" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="B142" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="C142" s="26" t="s">
+        <v>298</v>
+      </c>
+      <c r="D142" s="27" t="s">
         <v>316</v>
       </c>
-      <c r="F141" s="10" t="s">
+      <c r="E142" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="F142" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="G141" s="11"/>
-      <c r="H141" s="11"/>
-      <c r="I141" s="12"/>
-    </row>
-    <row r="142" spans="1:9">
-      <c r="A142" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B142" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="C142" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="D142" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="E142" s="9" t="s">
+      <c r="G142" s="25"/>
+      <c r="H142" s="22"/>
+      <c r="I142" s="12"/>
+    </row>
+    <row r="143" spans="1:9">
+      <c r="A143" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B143" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="C143" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="D143" s="12" t="s">
         <v>318</v>
       </c>
-      <c r="F142" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G142" s="11"/>
-      <c r="H142" s="11"/>
-      <c r="I142" s="12"/>
-    </row>
-    <row r="143" spans="1:9">
-      <c r="A143" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B143" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="C143" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="D143" s="8" t="s">
+      <c r="E143" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="E143" s="9" t="s">
+      <c r="F143" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G143" s="25"/>
+      <c r="H143" s="22"/>
+      <c r="I143" s="12"/>
+    </row>
+    <row r="144" spans="1:9">
+      <c r="A144" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B144" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="C144" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="D144" s="12" t="s">
         <v>320</v>
       </c>
-      <c r="F143" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G143" s="11"/>
-      <c r="H143" s="11"/>
-      <c r="I143" s="12"/>
-    </row>
-    <row r="144" spans="1:9">
-      <c r="A144" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B144" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="C144" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="D144" s="8" t="s">
+      <c r="E144" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="E144" s="9" t="s">
+      <c r="F144" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G144" s="22"/>
+      <c r="H144" s="22"/>
+      <c r="I144" s="12"/>
+    </row>
+    <row r="145" spans="1:9">
+      <c r="A145" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B145" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="C145" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="D145" s="12" t="s">
         <v>322</v>
       </c>
-      <c r="F144" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G144" s="11"/>
-      <c r="H144" s="11"/>
-      <c r="I144" s="12"/>
-    </row>
-    <row r="145" spans="1:9">
-      <c r="A145" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B145" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="C145" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="D145" s="8" t="s">
+      <c r="E145" s="12" t="s">
         <v>323</v>
       </c>
-      <c r="E145" s="9" t="s">
+      <c r="F145" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G145" s="22"/>
+      <c r="H145" s="22"/>
+      <c r="I145" s="12"/>
+    </row>
+    <row r="146" spans="1:9">
+      <c r="A146" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B146" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="C146" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="D146" s="12" t="s">
         <v>324</v>
       </c>
-      <c r="F145" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G145" s="11"/>
-      <c r="H145" s="11"/>
-      <c r="I145" s="12"/>
-    </row>
-    <row r="146" spans="1:9">
-      <c r="A146" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B146" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="C146" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="D146" s="8" t="s">
+      <c r="E146" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="E146" s="9" t="s">
+      <c r="F146" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G146" s="22"/>
+      <c r="H146" s="22"/>
+      <c r="I146" s="12"/>
+    </row>
+    <row r="147" spans="1:9">
+      <c r="A147" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B147" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="C147" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="D147" s="12" t="s">
         <v>326</v>
       </c>
-      <c r="F146" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G146" s="11"/>
-      <c r="H146" s="11"/>
-      <c r="I146" s="12"/>
-    </row>
-    <row r="147" spans="1:9">
-      <c r="A147" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B147" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="C147" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="D147" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E147" s="9" t="s">
-        <v>36</v>
+      <c r="E147" s="12" t="s">
+        <v>327</v>
       </c>
       <c r="F147" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="G147" s="11"/>
-      <c r="H147" s="11"/>
+        <v>60</v>
+      </c>
+      <c r="G147" s="22"/>
+      <c r="H147" s="22"/>
       <c r="I147" s="12"/>
     </row>
     <row r="148" spans="1:9">
       <c r="A148" s="8" t="s">
-        <v>292</v>
+        <v>9</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>293</v>
+        <v>328</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>294</v>
+        <v>329</v>
       </c>
       <c r="D148" s="8" t="s">
-        <v>327</v>
+        <v>12</v>
       </c>
       <c r="E148" s="9" t="s">
-        <v>328</v>
+        <v>13</v>
       </c>
       <c r="F148" s="10" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G148" s="11"/>
-      <c r="H148" s="11"/>
+      <c r="H148" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="I148" s="12"/>
     </row>
     <row r="149" spans="1:9">
       <c r="A149" s="8" t="s">
-        <v>292</v>
+        <v>9</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>293</v>
+        <v>328</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>294</v>
+        <v>329</v>
       </c>
       <c r="D149" s="8" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>330</v>
+        <v>156</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G149" s="11"/>
-      <c r="H149" s="11"/>
+      <c r="G149" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H149" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="I149" s="12"/>
     </row>
     <row r="150" spans="1:9">
       <c r="A150" s="8" t="s">
-        <v>292</v>
+        <v>9</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>293</v>
+        <v>328</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>294</v>
+        <v>329</v>
       </c>
       <c r="D150" s="8" t="s">
         <v>331</v>
@@ -6557,30 +6575,32 @@
         <v>332</v>
       </c>
       <c r="F150" s="10" t="s">
-        <v>14</v>
+        <v>333</v>
       </c>
       <c r="G150" s="11"/>
       <c r="H150" s="11"/>
-      <c r="I150" s="12"/>
+      <c r="I150" s="12" t="s">
+        <v>334</v>
+      </c>
     </row>
     <row r="151" spans="1:9">
       <c r="A151" s="8" t="s">
-        <v>292</v>
+        <v>9</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>293</v>
+        <v>328</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>294</v>
+        <v>329</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>333</v>
+        <v>302</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="F151" s="10" t="s">
-        <v>14</v>
+        <v>303</v>
+      </c>
+      <c r="F151" s="25" t="s">
+        <v>152</v>
       </c>
       <c r="G151" s="11"/>
       <c r="H151" s="11"/>
@@ -6588,95 +6608,93 @@
     </row>
     <row r="152" spans="1:9">
       <c r="A152" s="8" t="s">
-        <v>292</v>
+        <v>9</v>
       </c>
       <c r="B152" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="C152" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="D152" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="C152" s="25" t="s">
+      <c r="E152" s="9" t="s">
         <v>336</v>
-      </c>
-      <c r="D152" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="E152" s="9" t="s">
-        <v>296</v>
       </c>
       <c r="F152" s="10" t="s">
         <v>14</v>
       </c>
       <c r="G152" s="11"/>
-      <c r="H152" s="11" t="s">
-        <v>15</v>
-      </c>
+      <c r="H152" s="11"/>
       <c r="I152" s="12"/>
     </row>
     <row r="153" spans="1:9">
       <c r="A153" s="8" t="s">
-        <v>292</v>
+        <v>9</v>
       </c>
       <c r="B153" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="C153" s="25" t="s">
-        <v>336</v>
+        <v>328</v>
+      </c>
+      <c r="C153" s="8" t="s">
+        <v>329</v>
       </c>
       <c r="D153" s="8" t="s">
         <v>337</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>156</v>
+        <v>338</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G153" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="H153" s="22"/>
+      <c r="G153" s="11"/>
+      <c r="H153" s="11"/>
       <c r="I153" s="12"/>
     </row>
     <row r="154" spans="1:9">
       <c r="A154" s="8" t="s">
-        <v>292</v>
+        <v>339</v>
       </c>
       <c r="B154" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="C154" s="25" t="s">
-        <v>336</v>
+        <v>340</v>
+      </c>
+      <c r="C154" s="8" t="s">
+        <v>341</v>
       </c>
       <c r="D154" s="8" t="s">
-        <v>157</v>
+        <v>342</v>
       </c>
       <c r="E154" s="9" t="s">
-        <v>158</v>
+        <v>343</v>
       </c>
       <c r="F154" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G154" s="11"/>
+        <v>14</v>
+      </c>
+      <c r="G154" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="H154" s="11"/>
       <c r="I154" s="12"/>
     </row>
     <row r="155" spans="1:9">
       <c r="A155" s="8" t="s">
-        <v>292</v>
+        <v>339</v>
       </c>
       <c r="B155" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="C155" s="25" t="s">
-        <v>336</v>
+        <v>340</v>
+      </c>
+      <c r="C155" s="8" t="s">
+        <v>341</v>
       </c>
       <c r="D155" s="8" t="s">
-        <v>159</v>
+        <v>344</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>160</v>
+        <v>345</v>
       </c>
       <c r="F155" s="10" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G155" s="11"/>
       <c r="H155" s="11"/>
@@ -6684,65 +6702,67 @@
     </row>
     <row r="156" spans="1:9">
       <c r="A156" s="8" t="s">
-        <v>292</v>
+        <v>339</v>
       </c>
       <c r="B156" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="C156" s="25" t="s">
-        <v>336</v>
+        <v>340</v>
+      </c>
+      <c r="C156" s="8" t="s">
+        <v>341</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>161</v>
+        <v>346</v>
       </c>
       <c r="E156" s="9" t="s">
-        <v>162</v>
+        <v>347</v>
       </c>
       <c r="F156" s="10" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G156" s="11"/>
       <c r="H156" s="11"/>
       <c r="I156" s="12"/>
     </row>
     <row r="157" spans="1:9">
-      <c r="A157" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B157" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="C157" s="25" t="s">
-        <v>336</v>
-      </c>
-      <c r="D157" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="E157" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="F157" s="10" t="s">
+      <c r="A157" s="29" t="s">
+        <v>339</v>
+      </c>
+      <c r="B157" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="C157" s="29" t="s">
+        <v>341</v>
+      </c>
+      <c r="D157" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="E157" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F157" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="G157" s="11"/>
-      <c r="H157" s="11"/>
+      <c r="G157" s="31"/>
+      <c r="H157" s="31" t="s">
+        <v>15</v>
+      </c>
       <c r="I157" s="12"/>
     </row>
     <row r="158" spans="1:9">
       <c r="A158" s="8" t="s">
-        <v>292</v>
+        <v>339</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="C158" s="25" t="s">
-        <v>336</v>
+        <v>340</v>
+      </c>
+      <c r="C158" s="8" t="s">
+        <v>341</v>
       </c>
       <c r="D158" s="8" t="s">
-        <v>165</v>
+        <v>16</v>
       </c>
       <c r="E158" s="9" t="s">
-        <v>166</v>
+        <v>348</v>
       </c>
       <c r="F158" s="10" t="s">
         <v>14</v>
@@ -6753,721 +6773,715 @@
     </row>
     <row r="159" spans="1:9">
       <c r="A159" s="8" t="s">
-        <v>292</v>
+        <v>339</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="C159" s="25" t="s">
-        <v>336</v>
+        <v>340</v>
+      </c>
+      <c r="C159" s="8" t="s">
+        <v>341</v>
       </c>
       <c r="D159" s="8" t="s">
-        <v>167</v>
+        <v>349</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>168</v>
+        <v>350</v>
       </c>
       <c r="F159" s="10" t="s">
-        <v>152</v>
+        <v>30</v>
       </c>
       <c r="G159" s="11"/>
       <c r="H159" s="11"/>
       <c r="I159" s="12"/>
     </row>
     <row r="160" spans="1:9">
-      <c r="A160" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="B160" s="25" t="s">
-        <v>335</v>
-      </c>
-      <c r="C160" s="25" t="s">
-        <v>336</v>
-      </c>
-      <c r="D160" s="25" t="s">
-        <v>338</v>
-      </c>
-      <c r="E160" s="26" t="s">
+      <c r="A160" s="8" t="s">
         <v>339</v>
       </c>
-      <c r="F160" s="27" t="s">
-        <v>60</v>
+      <c r="B160" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="C160" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="D160" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="E160" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="F160" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="G160" s="11"/>
       <c r="H160" s="11"/>
       <c r="I160" s="12"/>
     </row>
     <row r="161" spans="1:9">
-      <c r="A161" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="B161" s="25" t="s">
-        <v>335</v>
-      </c>
-      <c r="C161" s="28" t="s">
-        <v>336</v>
-      </c>
-      <c r="D161" s="28" t="s">
+      <c r="A161" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B161" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="E161" s="26" t="s">
+      <c r="C161" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="F161" s="27" t="s">
-        <v>86</v>
+      <c r="D161" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="E161" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="F161" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="G161" s="11"/>
       <c r="H161" s="11"/>
       <c r="I161" s="12"/>
     </row>
     <row r="162" spans="1:9">
-      <c r="A162" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="B162" s="25" t="s">
-        <v>335</v>
-      </c>
-      <c r="C162" s="28" t="s">
-        <v>336</v>
-      </c>
-      <c r="D162" s="28" t="s">
-        <v>342</v>
-      </c>
-      <c r="E162" s="26" t="s">
-        <v>343</v>
-      </c>
-      <c r="F162" s="27" t="s">
-        <v>60</v>
+      <c r="A162" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B162" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="C162" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="D162" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="E162" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="F162" s="10" t="s">
+        <v>357</v>
       </c>
       <c r="G162" s="11"/>
       <c r="H162" s="11"/>
       <c r="I162" s="12"/>
     </row>
     <row r="163" spans="1:9">
-      <c r="A163" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="B163" s="20" t="s">
-        <v>335</v>
-      </c>
-      <c r="C163" s="29" t="s">
-        <v>336</v>
-      </c>
-      <c r="D163" s="30" t="s">
-        <v>344</v>
-      </c>
-      <c r="E163" s="30" t="s">
-        <v>345</v>
-      </c>
-      <c r="F163" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="G163" s="22"/>
-      <c r="H163" s="22"/>
+      <c r="A163" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B163" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="C163" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="D163" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="E163" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="F163" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G163" s="11"/>
+      <c r="H163" s="11"/>
       <c r="I163" s="12"/>
     </row>
     <row r="164" spans="1:9">
-      <c r="A164" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="B164" s="20" t="s">
-        <v>335</v>
-      </c>
-      <c r="C164" s="29" t="s">
-        <v>336</v>
-      </c>
-      <c r="D164" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="E164" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="F164" s="31" t="s">
-        <v>86</v>
-      </c>
-      <c r="G164" s="22"/>
-      <c r="H164" s="22"/>
+      <c r="A164" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B164" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="C164" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="D164" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E164" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F164" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G164" s="11"/>
+      <c r="H164" s="11"/>
       <c r="I164" s="12"/>
     </row>
     <row r="165" spans="1:9">
-      <c r="A165" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="B165" s="20" t="s">
-        <v>335</v>
-      </c>
-      <c r="C165" s="29" t="s">
-        <v>336</v>
-      </c>
-      <c r="D165" s="29" t="s">
-        <v>346</v>
-      </c>
-      <c r="E165" s="21" t="s">
-        <v>347</v>
-      </c>
-      <c r="F165" s="31" t="s">
-        <v>60</v>
+      <c r="A165" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B165" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="C165" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="D165" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E165" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F165" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="G165" s="11"/>
       <c r="H165" s="11"/>
       <c r="I165" s="12"/>
     </row>
     <row r="166" spans="1:9">
-      <c r="A166" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B166" s="32" t="s">
-        <v>348</v>
-      </c>
-      <c r="C166" s="32" t="s">
-        <v>349</v>
-      </c>
-      <c r="D166" s="32" t="s">
-        <v>12</v>
+      <c r="A166" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B166" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="C166" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="D166" s="8" t="s">
+        <v>360</v>
       </c>
       <c r="E166" s="9" t="s">
-        <v>13</v>
+        <v>361</v>
       </c>
       <c r="F166" s="10" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G166" s="11"/>
-      <c r="H166" s="11" t="s">
-        <v>15</v>
-      </c>
+      <c r="H166" s="11"/>
       <c r="I166" s="12"/>
     </row>
     <row r="167" spans="1:9">
-      <c r="A167" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B167" s="32" t="s">
-        <v>348</v>
-      </c>
-      <c r="C167" s="32" t="s">
-        <v>349</v>
-      </c>
-      <c r="D167" s="32" t="s">
-        <v>155</v>
+      <c r="A167" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B167" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="C167" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="D167" s="8" t="s">
+        <v>362</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>156</v>
+        <v>363</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>14</v>
       </c>
       <c r="G167" s="11"/>
-      <c r="H167" s="11" t="s">
-        <v>15</v>
-      </c>
+      <c r="H167" s="11"/>
       <c r="I167" s="12"/>
     </row>
     <row r="168" spans="1:9">
-      <c r="A168" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B168" s="32" t="s">
-        <v>348</v>
-      </c>
-      <c r="C168" s="32" t="s">
-        <v>349</v>
-      </c>
-      <c r="D168" s="32" t="s">
-        <v>350</v>
-      </c>
-      <c r="E168" s="32" t="s">
-        <v>351</v>
+      <c r="A168" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B168" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="C168" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="D168" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="E168" s="9" t="s">
+        <v>365</v>
       </c>
       <c r="F168" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G168" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H168" s="22"/>
+      <c r="G168" s="11"/>
+      <c r="H168" s="11"/>
       <c r="I168" s="12"/>
     </row>
     <row r="169" spans="1:9">
-      <c r="A169" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B169" s="32" t="s">
-        <v>348</v>
-      </c>
-      <c r="C169" s="32" t="s">
-        <v>349</v>
-      </c>
-      <c r="D169" s="32" t="s">
-        <v>352</v>
-      </c>
-      <c r="E169" s="32" t="s">
-        <v>353</v>
-      </c>
-      <c r="F169" s="32" t="s">
+      <c r="A169" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B169" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="C169" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="D169" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="E169" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="F169" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G169" s="32"/>
-      <c r="H169" s="22"/>
+      <c r="G169" s="11"/>
+      <c r="H169" s="11"/>
       <c r="I169" s="12"/>
     </row>
     <row r="170" spans="1:9">
-      <c r="A170" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B170" s="32" t="s">
-        <v>348</v>
-      </c>
-      <c r="C170" s="32" t="s">
-        <v>349</v>
-      </c>
-      <c r="D170" s="32" t="s">
-        <v>354</v>
-      </c>
-      <c r="E170" s="32" t="s">
-        <v>355</v>
-      </c>
-      <c r="F170" s="32" t="s">
+      <c r="A170" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B170" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="C170" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="D170" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="E170" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="F170" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G170" s="32"/>
-      <c r="H170" s="22"/>
+      <c r="G170" s="11"/>
+      <c r="H170" s="11"/>
       <c r="I170" s="12"/>
     </row>
     <row r="171" spans="1:9">
-      <c r="A171" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B171" s="32" t="s">
-        <v>348</v>
-      </c>
-      <c r="C171" s="32" t="s">
-        <v>349</v>
-      </c>
-      <c r="D171" s="32" t="s">
-        <v>356</v>
-      </c>
-      <c r="E171" s="32" t="s">
-        <v>357</v>
-      </c>
-      <c r="F171" s="32" t="s">
+      <c r="A171" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B171" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="C171" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="D171" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="E171" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="F171" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G171" s="32"/>
-      <c r="H171" s="22"/>
+      <c r="G171" s="11"/>
+      <c r="H171" s="11"/>
       <c r="I171" s="12"/>
     </row>
     <row r="172" spans="1:9">
-      <c r="A172" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B172" s="32" t="s">
-        <v>348</v>
-      </c>
-      <c r="C172" s="32" t="s">
-        <v>349</v>
-      </c>
-      <c r="D172" s="32" t="s">
-        <v>358</v>
-      </c>
-      <c r="E172" s="32" t="s">
-        <v>359</v>
-      </c>
-      <c r="F172" s="32" t="s">
+      <c r="A172" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B172" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="C172" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="D172" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="E172" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="F172" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G172" s="32"/>
-      <c r="H172" s="22"/>
+      <c r="G172" s="11"/>
+      <c r="H172" s="11"/>
       <c r="I172" s="12"/>
     </row>
     <row r="173" spans="1:9">
-      <c r="A173" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B173" s="32" t="s">
-        <v>348</v>
-      </c>
-      <c r="C173" s="32" t="s">
-        <v>349</v>
-      </c>
-      <c r="D173" s="32" t="s">
-        <v>360</v>
-      </c>
-      <c r="E173" s="32" t="s">
-        <v>361</v>
-      </c>
-      <c r="F173" s="32" t="s">
+      <c r="A173" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B173" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="C173" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="D173" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E173" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F173" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="G173" s="11"/>
+      <c r="H173" s="11"/>
+      <c r="I173" s="12"/>
+    </row>
+    <row r="174" spans="1:9">
+      <c r="A174" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B174" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="C174" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="D174" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="E174" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="F174" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G174" s="11"/>
+      <c r="H174" s="11"/>
+      <c r="I174" s="12"/>
+    </row>
+    <row r="175" spans="1:9">
+      <c r="A175" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B175" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="C175" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="D175" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="E175" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="F175" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G173" s="32"/>
-      <c r="H173" s="22"/>
-      <c r="I173" s="12"/>
-    </row>
-    <row r="174" spans="1:9">
-      <c r="A174" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B174" s="32" t="s">
-        <v>348</v>
-      </c>
-      <c r="C174" s="32" t="s">
-        <v>349</v>
-      </c>
-      <c r="D174" s="32" t="s">
-        <v>362</v>
-      </c>
-      <c r="E174" s="32" t="s">
-        <v>363</v>
-      </c>
-      <c r="F174" s="32" t="s">
-        <v>152</v>
-      </c>
-      <c r="G174" s="32"/>
-      <c r="H174" s="22"/>
-      <c r="I174" s="12"/>
-    </row>
-    <row r="175" spans="1:9">
-      <c r="A175" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B175" s="32" t="s">
-        <v>348</v>
-      </c>
-      <c r="C175" s="32" t="s">
-        <v>349</v>
-      </c>
-      <c r="D175" s="32" t="s">
-        <v>364</v>
-      </c>
-      <c r="E175" s="32" t="s">
-        <v>365</v>
-      </c>
-      <c r="F175" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="G175" s="32"/>
-      <c r="H175" s="22"/>
+      <c r="G175" s="11"/>
+      <c r="H175" s="11"/>
       <c r="I175" s="12"/>
     </row>
     <row r="176" spans="1:9">
-      <c r="A176" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B176" s="32" t="s">
-        <v>366</v>
-      </c>
-      <c r="C176" s="32" t="s">
-        <v>367</v>
-      </c>
-      <c r="D176" s="32" t="s">
-        <v>368</v>
-      </c>
-      <c r="E176" s="32" t="s">
-        <v>351</v>
+      <c r="A176" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B176" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="C176" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="D176" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="E176" s="9" t="s">
+        <v>380</v>
       </c>
       <c r="F176" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G176" s="32"/>
-      <c r="H176" s="22" t="s">
-        <v>15</v>
-      </c>
+      <c r="G176" s="11"/>
+      <c r="H176" s="11"/>
       <c r="I176" s="12"/>
     </row>
     <row r="177" spans="1:9">
-      <c r="A177" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B177" s="32" t="s">
-        <v>366</v>
-      </c>
-      <c r="C177" s="32" t="s">
-        <v>367</v>
-      </c>
-      <c r="D177" s="32" t="s">
-        <v>369</v>
-      </c>
-      <c r="E177" s="32" t="s">
-        <v>370</v>
+      <c r="A177" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B177" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="C177" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="D177" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="E177" s="9" t="s">
+        <v>382</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G177" s="32" t="s">
+      <c r="G177" s="11"/>
+      <c r="H177" s="11"/>
+      <c r="I177" s="12"/>
+    </row>
+    <row r="178" spans="1:9">
+      <c r="A178" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B178" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="C178" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="D178" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="E178" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="F178" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G178" s="11"/>
+      <c r="H178" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H177" s="22"/>
-      <c r="I177" s="12"/>
-    </row>
-    <row r="178" spans="1:9">
-      <c r="A178" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B178" s="32" t="s">
-        <v>366</v>
-      </c>
-      <c r="C178" s="32" t="s">
-        <v>367</v>
-      </c>
-      <c r="D178" s="32" t="s">
-        <v>285</v>
-      </c>
-      <c r="E178" s="32" t="s">
-        <v>286</v>
-      </c>
-      <c r="F178" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="G178" s="32"/>
-      <c r="H178" s="22"/>
       <c r="I178" s="12"/>
     </row>
     <row r="179" spans="1:9">
-      <c r="A179" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B179" s="32" t="s">
-        <v>366</v>
-      </c>
-      <c r="C179" s="32" t="s">
-        <v>367</v>
-      </c>
-      <c r="D179" s="32" t="s">
-        <v>371</v>
-      </c>
-      <c r="E179" s="32" t="s">
-        <v>372</v>
-      </c>
-      <c r="F179" s="32" t="s">
+      <c r="A179" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B179" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="C179" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="D179" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="E179" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F179" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G179" s="32"/>
+      <c r="G179" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="H179" s="22"/>
       <c r="I179" s="12"/>
     </row>
     <row r="180" spans="1:9">
-      <c r="A180" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B180" s="32" t="s">
-        <v>366</v>
-      </c>
-      <c r="C180" s="32" t="s">
-        <v>367</v>
-      </c>
-      <c r="D180" s="32" t="s">
-        <v>373</v>
-      </c>
-      <c r="E180" s="32" t="s">
-        <v>374</v>
-      </c>
-      <c r="F180" s="32" t="s">
+      <c r="A180" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B180" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="C180" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="D180" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="E180" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F180" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G180" s="11"/>
+      <c r="H180" s="11"/>
+      <c r="I180" s="12"/>
+    </row>
+    <row r="181" spans="1:9">
+      <c r="A181" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B181" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="C181" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="D181" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="E181" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F181" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G181" s="11"/>
+      <c r="H181" s="11"/>
+      <c r="I181" s="12"/>
+    </row>
+    <row r="182" spans="1:9">
+      <c r="A182" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B182" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="C182" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="D182" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E182" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F182" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G182" s="11"/>
+      <c r="H182" s="11"/>
+      <c r="I182" s="12"/>
+    </row>
+    <row r="183" spans="1:9">
+      <c r="A183" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B183" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="C183" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="D183" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="E183" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="F183" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G180" s="32"/>
-      <c r="H180" s="22"/>
-      <c r="I180" s="12"/>
-    </row>
-    <row r="181" spans="1:9">
-      <c r="A181" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B181" s="32" t="s">
-        <v>366</v>
-      </c>
-      <c r="C181" s="32" t="s">
-        <v>367</v>
-      </c>
-      <c r="D181" s="32" t="s">
-        <v>375</v>
-      </c>
-      <c r="E181" s="32" t="s">
-        <v>376</v>
-      </c>
-      <c r="F181" s="32" t="s">
+      <c r="G183" s="11"/>
+      <c r="H183" s="11"/>
+      <c r="I183" s="12"/>
+    </row>
+    <row r="184" spans="1:9">
+      <c r="A184" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B184" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="C184" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="D184" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="E184" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F184" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G181" s="32"/>
-      <c r="H181" s="22"/>
-      <c r="I181" s="12"/>
-    </row>
-    <row r="182" spans="1:9">
-      <c r="A182" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B182" s="32" t="s">
-        <v>366</v>
-      </c>
-      <c r="C182" s="32" t="s">
-        <v>367</v>
-      </c>
-      <c r="D182" s="32" t="s">
-        <v>377</v>
-      </c>
-      <c r="E182" s="32" t="s">
-        <v>378</v>
-      </c>
-      <c r="F182" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="G182" s="32"/>
-      <c r="H182" s="22"/>
-      <c r="I182" s="12"/>
-    </row>
-    <row r="183" spans="1:9">
-      <c r="A183" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B183" s="32" t="s">
-        <v>366</v>
-      </c>
-      <c r="C183" s="32" t="s">
-        <v>367</v>
-      </c>
-      <c r="D183" s="32" t="s">
-        <v>379</v>
-      </c>
-      <c r="E183" s="32" t="s">
-        <v>380</v>
-      </c>
-      <c r="F183" s="32" t="s">
+      <c r="G184" s="11"/>
+      <c r="H184" s="11"/>
+      <c r="I184" s="12"/>
+    </row>
+    <row r="185" spans="1:9">
+      <c r="A185" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B185" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="C185" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="D185" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="E185" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F185" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="G183" s="32"/>
-      <c r="H183" s="22"/>
-      <c r="I183" s="12"/>
-    </row>
-    <row r="184" spans="1:9">
-      <c r="A184" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B184" s="32" t="s">
-        <v>366</v>
-      </c>
-      <c r="C184" s="32" t="s">
-        <v>367</v>
-      </c>
-      <c r="D184" s="32" t="s">
-        <v>381</v>
-      </c>
-      <c r="E184" s="32" t="s">
-        <v>382</v>
-      </c>
-      <c r="F184" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="G184" s="32"/>
-      <c r="H184" s="22"/>
-      <c r="I184" s="12"/>
-    </row>
-    <row r="185" spans="1:9">
-      <c r="A185" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="B185" s="33" t="s">
-        <v>366</v>
-      </c>
-      <c r="C185" s="33" t="s">
-        <v>367</v>
-      </c>
-      <c r="D185" s="34" t="s">
-        <v>383</v>
-      </c>
-      <c r="E185" s="34" t="s">
-        <v>384</v>
-      </c>
-      <c r="F185" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="G185" s="32"/>
-      <c r="H185" s="22"/>
+      <c r="G185" s="11"/>
+      <c r="H185" s="11"/>
       <c r="I185" s="12"/>
     </row>
     <row r="186" spans="1:9">
       <c r="A186" s="32" t="s">
-        <v>9</v>
+        <v>339</v>
       </c>
       <c r="B186" s="32" t="s">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="C186" s="32" t="s">
-        <v>367</v>
-      </c>
-      <c r="D186" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="E186" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="D186" s="32" t="s">
         <v>386</v>
       </c>
-      <c r="F186" s="10" t="s">
+      <c r="E186" s="33" t="s">
+        <v>387</v>
+      </c>
+      <c r="F186" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="G186" s="32"/>
-      <c r="H186" s="22"/>
+      <c r="G186" s="11"/>
+      <c r="H186" s="11"/>
       <c r="I186" s="12"/>
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="32" t="s">
-        <v>9</v>
+        <v>339</v>
       </c>
       <c r="B187" s="32" t="s">
-        <v>366</v>
-      </c>
-      <c r="C187" s="32" t="s">
-        <v>367</v>
-      </c>
-      <c r="D187" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="E187" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="C187" s="35" t="s">
+        <v>384</v>
+      </c>
+      <c r="D187" s="35" t="s">
         <v>388</v>
       </c>
-      <c r="F187" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G187" s="22"/>
-      <c r="H187" s="22"/>
+      <c r="E187" s="33" t="s">
+        <v>389</v>
+      </c>
+      <c r="F187" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="G187" s="11"/>
+      <c r="H187" s="11"/>
       <c r="I187" s="12"/>
     </row>
     <row r="188" spans="1:9">
       <c r="A188" s="32" t="s">
-        <v>9</v>
+        <v>339</v>
       </c>
       <c r="B188" s="32" t="s">
-        <v>366</v>
-      </c>
-      <c r="C188" s="32" t="s">
-        <v>367</v>
-      </c>
-      <c r="D188" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="E188" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="C188" s="35" t="s">
+        <v>384</v>
+      </c>
+      <c r="D188" s="35" t="s">
         <v>390</v>
       </c>
-      <c r="F188" s="10" t="s">
+      <c r="E188" s="33" t="s">
+        <v>391</v>
+      </c>
+      <c r="F188" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="G188" s="22"/>
-      <c r="H188" s="22"/>
+      <c r="G188" s="11"/>
+      <c r="H188" s="11"/>
       <c r="I188" s="12"/>
     </row>
     <row r="189" spans="1:9">
-      <c r="A189" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B189" s="32" t="s">
-        <v>366</v>
-      </c>
-      <c r="C189" s="32" t="s">
-        <v>367</v>
-      </c>
-      <c r="D189" s="12" t="s">
-        <v>391</v>
-      </c>
-      <c r="E189" s="12" t="s">
+      <c r="A189" s="20" t="s">
+        <v>339</v>
+      </c>
+      <c r="B189" s="20" t="s">
+        <v>383</v>
+      </c>
+      <c r="C189" s="36" t="s">
+        <v>384</v>
+      </c>
+      <c r="D189" s="37" t="s">
         <v>392</v>
       </c>
-      <c r="F189" s="10" t="s">
+      <c r="E189" s="37" t="s">
+        <v>393</v>
+      </c>
+      <c r="F189" s="38" t="s">
         <v>60</v>
       </c>
       <c r="G189" s="22"/>
@@ -7475,64 +7489,66 @@
       <c r="I189" s="12"/>
     </row>
     <row r="190" spans="1:9">
-      <c r="A190" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B190" s="32" t="s">
-        <v>366</v>
-      </c>
-      <c r="C190" s="32" t="s">
-        <v>367</v>
-      </c>
-      <c r="D190" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="E190" s="12" t="s">
-        <v>394</v>
-      </c>
-      <c r="F190" s="10" t="s">
-        <v>60</v>
+      <c r="A190" s="20" t="s">
+        <v>339</v>
+      </c>
+      <c r="B190" s="20" t="s">
+        <v>383</v>
+      </c>
+      <c r="C190" s="36" t="s">
+        <v>384</v>
+      </c>
+      <c r="D190" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="E190" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="F190" s="38" t="s">
+        <v>86</v>
       </c>
       <c r="G190" s="22"/>
       <c r="H190" s="22"/>
       <c r="I190" s="12"/>
     </row>
     <row r="191" spans="1:9">
-      <c r="A191" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B191" s="36" t="s">
-        <v>348</v>
-      </c>
-      <c r="C191" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D191" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="E191" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="F191" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G191" s="4"/>
+      <c r="A191" s="20" t="s">
+        <v>339</v>
+      </c>
+      <c r="B191" s="20" t="s">
+        <v>383</v>
+      </c>
+      <c r="C191" s="36" t="s">
+        <v>384</v>
+      </c>
+      <c r="D191" s="36" t="s">
+        <v>394</v>
+      </c>
+      <c r="E191" s="21" t="s">
+        <v>395</v>
+      </c>
+      <c r="F191" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="G191" s="11"/>
+      <c r="H191" s="11"/>
+      <c r="I191" s="12"/>
     </row>
     <row r="192" spans="1:9">
       <c r="A192" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B192" s="36" t="s">
-        <v>348</v>
+      <c r="B192" s="39" t="s">
+        <v>279</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D192" s="36" t="s">
-        <v>356</v>
+        <v>280</v>
+      </c>
+      <c r="D192" s="39" t="s">
+        <v>287</v>
       </c>
       <c r="E192" s="4" t="s">
-        <v>357</v>
+        <v>288</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>14</v>
@@ -7543,17 +7559,17 @@
       <c r="A193" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B193" s="36" t="s">
-        <v>348</v>
+      <c r="B193" s="39" t="s">
+        <v>279</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D193" s="36" t="s">
-        <v>358</v>
+        <v>280</v>
+      </c>
+      <c r="D193" s="39" t="s">
+        <v>289</v>
       </c>
       <c r="E193" s="4" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>14</v>
@@ -7564,17 +7580,17 @@
       <c r="A194" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B194" s="36" t="s">
-        <v>348</v>
+      <c r="B194" s="39" t="s">
+        <v>279</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D194" s="36" t="s">
-        <v>360</v>
+        <v>280</v>
+      </c>
+      <c r="D194" s="39" t="s">
+        <v>291</v>
       </c>
       <c r="E194" s="4" t="s">
-        <v>361</v>
+        <v>292</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>14</v>
@@ -7585,17 +7601,17 @@
       <c r="A195" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B195" s="36" t="s">
-        <v>348</v>
+      <c r="B195" s="39" t="s">
+        <v>279</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D195" s="36" t="s">
-        <v>362</v>
+        <v>280</v>
+      </c>
+      <c r="D195" s="39" t="s">
+        <v>293</v>
       </c>
       <c r="E195" s="4" t="s">
-        <v>363</v>
+        <v>294</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>152</v>
@@ -7606,17 +7622,17 @@
       <c r="A196" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B196" s="36" t="s">
-        <v>348</v>
+      <c r="B196" s="39" t="s">
+        <v>279</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D196" s="36" t="s">
-        <v>364</v>
+        <v>280</v>
+      </c>
+      <c r="D196" s="39" t="s">
+        <v>295</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>365</v>
+        <v>296</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>14</v>
@@ -7627,23 +7643,23 @@
       <c r="A197" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B197" s="36" t="s">
-        <v>366</v>
+      <c r="B197" s="39" t="s">
+        <v>297</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>367</v>
+        <v>298</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>368</v>
+        <v>299</v>
       </c>
       <c r="E197" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="F197" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="F197" s="40" t="s">
         <v>14</v>
       </c>
       <c r="G197" s="4"/>
-      <c r="H197" s="38" t="s">
+      <c r="H197" s="41" t="s">
         <v>15</v>
       </c>
     </row>
@@ -7651,19 +7667,19 @@
       <c r="A198" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B198" s="36" t="s">
-        <v>366</v>
+      <c r="B198" s="39" t="s">
+        <v>297</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>367</v>
+        <v>298</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>369</v>
+        <v>300</v>
       </c>
       <c r="E198" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="F198" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="F198" s="40" t="s">
         <v>14</v>
       </c>
       <c r="G198" s="4" t="s">
@@ -7674,17 +7690,17 @@
       <c r="A199" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B199" s="36" t="s">
-        <v>366</v>
+      <c r="B199" s="39" t="s">
+        <v>297</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="D199" s="36" t="s">
-        <v>285</v>
+        <v>298</v>
+      </c>
+      <c r="D199" s="39" t="s">
+        <v>302</v>
       </c>
       <c r="E199" s="4" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="F199" s="3" t="s">
         <v>44</v>
@@ -7695,17 +7711,17 @@
       <c r="A200" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B200" s="36" t="s">
-        <v>366</v>
+      <c r="B200" s="39" t="s">
+        <v>297</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>367</v>
+        <v>298</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>371</v>
+        <v>304</v>
       </c>
       <c r="E200" s="4" t="s">
-        <v>372</v>
+        <v>305</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>14</v>
@@ -7716,17 +7732,17 @@
       <c r="A201" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B201" s="36" t="s">
-        <v>366</v>
+      <c r="B201" s="39" t="s">
+        <v>297</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="D201" s="36" t="s">
-        <v>373</v>
+        <v>298</v>
+      </c>
+      <c r="D201" s="39" t="s">
+        <v>306</v>
       </c>
       <c r="E201" s="4" t="s">
-        <v>374</v>
+        <v>307</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>14</v>
@@ -7737,17 +7753,17 @@
       <c r="A202" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B202" s="36" t="s">
-        <v>366</v>
+      <c r="B202" s="39" t="s">
+        <v>297</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="D202" s="36" t="s">
-        <v>375</v>
+        <v>298</v>
+      </c>
+      <c r="D202" s="39" t="s">
+        <v>308</v>
       </c>
       <c r="E202" s="4" t="s">
-        <v>376</v>
+        <v>309</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>14</v>
@@ -7758,17 +7774,17 @@
       <c r="A203" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B203" s="36" t="s">
-        <v>366</v>
+      <c r="B203" s="39" t="s">
+        <v>297</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="D203" s="36" t="s">
-        <v>377</v>
+        <v>298</v>
+      </c>
+      <c r="D203" s="39" t="s">
+        <v>310</v>
       </c>
       <c r="E203" s="4" t="s">
-        <v>378</v>
+        <v>311</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>14</v>
@@ -7779,17 +7795,17 @@
       <c r="A204" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B204" s="36" t="s">
-        <v>366</v>
+      <c r="B204" s="39" t="s">
+        <v>297</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>367</v>
+        <v>298</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>379</v>
+        <v>312</v>
       </c>
       <c r="E204" s="4" t="s">
-        <v>380</v>
+        <v>313</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>152</v>
@@ -7800,17 +7816,17 @@
       <c r="A205" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B205" s="36" t="s">
-        <v>366</v>
+      <c r="B205" s="39" t="s">
+        <v>297</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>367</v>
+        <v>298</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>381</v>
+        <v>314</v>
       </c>
       <c r="E205" s="4" t="s">
-        <v>382</v>
+        <v>315</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>14</v>
@@ -7818,22 +7834,22 @@
       <c r="G205" s="4"/>
     </row>
     <row r="206" spans="1:8">
-      <c r="A206" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="B206" s="40" t="s">
-        <v>366</v>
-      </c>
-      <c r="C206" s="39" t="s">
-        <v>367</v>
-      </c>
-      <c r="D206" s="41" t="s">
-        <v>383</v>
-      </c>
-      <c r="E206" s="41" t="s">
-        <v>384</v>
-      </c>
-      <c r="F206" s="42" t="s">
+      <c r="A206" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B206" s="43" t="s">
+        <v>297</v>
+      </c>
+      <c r="C206" s="42" t="s">
+        <v>298</v>
+      </c>
+      <c r="D206" s="44" t="s">
+        <v>316</v>
+      </c>
+      <c r="E206" s="44" t="s">
+        <v>317</v>
+      </c>
+      <c r="F206" s="45" t="s">
         <v>14</v>
       </c>
       <c r="G206" s="4"/>
@@ -7842,19 +7858,19 @@
       <c r="A207" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B207" s="36" t="s">
-        <v>366</v>
+      <c r="B207" s="39" t="s">
+        <v>297</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="D207" s="43" t="s">
-        <v>385</v>
+        <v>298</v>
+      </c>
+      <c r="D207" s="46" t="s">
+        <v>318</v>
       </c>
       <c r="E207" t="s">
-        <v>386</v>
-      </c>
-      <c r="F207" s="44" t="s">
+        <v>319</v>
+      </c>
+      <c r="F207" s="47" t="s">
         <v>60</v>
       </c>
       <c r="G207" s="4"/>
@@ -7863,19 +7879,19 @@
       <c r="A208" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B208" s="36" t="s">
-        <v>366</v>
+      <c r="B208" s="39" t="s">
+        <v>297</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="D208" s="43" t="s">
-        <v>387</v>
+        <v>298</v>
+      </c>
+      <c r="D208" s="46" t="s">
+        <v>320</v>
       </c>
       <c r="E208" t="s">
-        <v>388</v>
-      </c>
-      <c r="F208" s="44" t="s">
+        <v>321</v>
+      </c>
+      <c r="F208" s="47" t="s">
         <v>60</v>
       </c>
     </row>
@@ -7883,19 +7899,19 @@
       <c r="A209" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B209" s="36" t="s">
-        <v>366</v>
+      <c r="B209" s="39" t="s">
+        <v>297</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="D209" s="43" t="s">
-        <v>389</v>
+        <v>298</v>
+      </c>
+      <c r="D209" s="46" t="s">
+        <v>322</v>
       </c>
       <c r="E209" t="s">
-        <v>390</v>
-      </c>
-      <c r="F209" s="44" t="s">
+        <v>323</v>
+      </c>
+      <c r="F209" s="47" t="s">
         <v>60</v>
       </c>
     </row>
@@ -7903,19 +7919,19 @@
       <c r="A210" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B210" s="36" t="s">
-        <v>366</v>
+      <c r="B210" s="39" t="s">
+        <v>297</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="D210" s="43" t="s">
-        <v>391</v>
+        <v>298</v>
+      </c>
+      <c r="D210" s="46" t="s">
+        <v>324</v>
       </c>
       <c r="E210" t="s">
-        <v>392</v>
-      </c>
-      <c r="F210" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="F210" s="47" t="s">
         <v>60</v>
       </c>
     </row>
@@ -7923,19 +7939,19 @@
       <c r="A211" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B211" s="36" t="s">
-        <v>366</v>
+      <c r="B211" s="39" t="s">
+        <v>297</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="D211" s="43" t="s">
-        <v>393</v>
+        <v>298</v>
+      </c>
+      <c r="D211" s="46" t="s">
+        <v>326</v>
       </c>
       <c r="E211" t="s">
-        <v>394</v>
-      </c>
-      <c r="F211" s="44" t="s">
+        <v>327</v>
+      </c>
+      <c r="F211" s="47" t="s">
         <v>60</v>
       </c>
     </row>
@@ -7967,13 +7983,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>6</v>
@@ -7982,21 +7998,21 @@
         <v>7</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2" ht="27" customHeight="1" spans="1:7">
       <c r="A2" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>15</v>
@@ -8007,13 +8023,13 @@
     <row r="3" ht="28.8" spans="1:7">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -8022,13 +8038,13 @@
     <row r="4" ht="28.8" spans="1:7">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -8037,10 +8053,10 @@
     <row r="5" ht="28.8" spans="1:7">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>361</v>
+        <v>292</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>165</v>
@@ -8052,13 +8068,13 @@
     <row r="6" ht="28.8" spans="1:7">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -8067,13 +8083,13 @@
     <row r="7" ht="28.8" spans="1:7">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -8082,13 +8098,13 @@
     <row r="8" ht="28.8" spans="1:7">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
@@ -8097,13 +8113,13 @@
     <row r="9" ht="28.8" spans="1:7">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>15</v>
@@ -8114,13 +8130,13 @@
     <row r="10" ht="28.8" spans="1:7">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -8129,13 +8145,13 @@
     <row r="11" ht="28.8" spans="1:7">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
@@ -8144,47 +8160,47 @@
     <row r="12" ht="57.6" spans="1:7">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="13" ht="72" spans="1:7">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G13" s="4"/>
     </row>
     <row r="14" ht="28.8" spans="1:7">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
@@ -8193,13 +8209,13 @@
     <row r="15" ht="43.2" spans="1:7">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>15</v>
@@ -8210,47 +8226,47 @@
     <row r="16" ht="57.6" spans="1:7">
       <c r="A16" s="4"/>
       <c r="B16" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>415</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>414</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G16" s="4"/>
     </row>
     <row r="17" ht="57.6" spans="1:7">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G17" s="4"/>
     </row>
     <row r="18" ht="43.2" spans="1:7">
       <c r="A18" s="4"/>
       <c r="B18" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -8259,13 +8275,13 @@
     <row r="19" ht="43.2" spans="1:7">
       <c r="A19" s="4"/>
       <c r="B19" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
@@ -8274,13 +8290,13 @@
     <row r="20" ht="28.8" spans="1:7">
       <c r="A20" s="4"/>
       <c r="B20" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>15</v>
@@ -8291,30 +8307,30 @@
     <row r="21" ht="13.5" customHeight="1" spans="1:7">
       <c r="A21" s="4"/>
       <c r="B21" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="22" ht="28.8" spans="1:7">
       <c r="A22" s="4"/>
       <c r="B22" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
@@ -8323,13 +8339,13 @@
     <row r="23" ht="28.8" spans="1:7">
       <c r="A23" s="4"/>
       <c r="B23" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
@@ -8338,13 +8354,13 @@
     <row r="24" ht="28.8" spans="1:7">
       <c r="A24" s="4"/>
       <c r="B24" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
@@ -8353,13 +8369,13 @@
     <row r="25" ht="28.8" spans="1:7">
       <c r="A25" s="4"/>
       <c r="B25" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -8368,13 +8384,13 @@
     <row r="26" ht="28.8" spans="1:7">
       <c r="A26" s="4"/>
       <c r="B26" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
@@ -8383,13 +8399,13 @@
     <row r="27" ht="28.8" spans="1:7">
       <c r="A27" s="4"/>
       <c r="B27" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -8398,13 +8414,13 @@
     <row r="28" ht="28.8" spans="1:7">
       <c r="A28" s="4"/>
       <c r="B28" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
@@ -8413,13 +8429,13 @@
     <row r="29" ht="28.8" spans="1:7">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
@@ -8428,13 +8444,13 @@
     <row r="30" ht="28.8" spans="1:7">
       <c r="A30" s="4"/>
       <c r="B30" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
@@ -8443,13 +8459,13 @@
     <row r="31" ht="28.8" spans="1:7">
       <c r="A31" s="4"/>
       <c r="B31" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
@@ -8458,13 +8474,13 @@
     <row r="32" ht="28.8" spans="1:7">
       <c r="A32" s="4"/>
       <c r="B32" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
@@ -8473,13 +8489,13 @@
     <row r="33" ht="28.8" spans="1:7">
       <c r="A33" s="4"/>
       <c r="B33" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
@@ -8487,16 +8503,16 @@
     </row>
     <row r="34" ht="27" customHeight="1" spans="1:7">
       <c r="A34" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>351</v>
+        <v>282</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>350</v>
+        <v>281</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>15</v>
@@ -8507,13 +8523,13 @@
     <row r="35" ht="28.8" spans="1:7">
       <c r="A35" s="4"/>
       <c r="B35" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>353</v>
+        <v>284</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>352</v>
+        <v>283</v>
       </c>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
@@ -8522,13 +8538,13 @@
     <row r="36" ht="28.8" spans="1:7">
       <c r="A36" s="4"/>
       <c r="B36" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>355</v>
+        <v>286</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>354</v>
+        <v>285</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
@@ -8537,13 +8553,13 @@
     <row r="37" ht="28.8" spans="1:7">
       <c r="A37" s="4"/>
       <c r="B37" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>357</v>
+        <v>288</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>356</v>
+        <v>287</v>
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
@@ -8552,13 +8568,13 @@
     <row r="38" ht="28.8" spans="1:7">
       <c r="A38" s="4"/>
       <c r="B38" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>358</v>
+        <v>289</v>
       </c>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
@@ -8567,13 +8583,13 @@
     <row r="39" ht="28.8" spans="1:7">
       <c r="A39" s="4"/>
       <c r="B39" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>361</v>
+        <v>292</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>360</v>
+        <v>291</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
@@ -8582,13 +8598,13 @@
     <row r="40" ht="28.8" spans="1:7">
       <c r="A40" s="4"/>
       <c r="B40" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>363</v>
+        <v>294</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>362</v>
+        <v>293</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
@@ -8597,13 +8613,13 @@
     <row r="41" ht="28.8" spans="1:7">
       <c r="A41" s="4"/>
       <c r="B41" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>365</v>
+        <v>296</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>364</v>
+        <v>295</v>
       </c>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
@@ -8612,13 +8628,13 @@
     <row r="42" ht="28.8" spans="1:7">
       <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
@@ -8627,13 +8643,13 @@
     <row r="43" ht="28.8" spans="1:7">
       <c r="A43" s="4"/>
       <c r="B43" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
@@ -8642,13 +8658,13 @@
     <row r="44" ht="28.8" spans="1:7">
       <c r="A44" s="4"/>
       <c r="B44" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
@@ -8657,13 +8673,13 @@
     <row r="45" ht="28.8" spans="1:7">
       <c r="A45" s="4"/>
       <c r="B45" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
@@ -8672,13 +8688,13 @@
     <row r="46" ht="28.8" spans="1:7">
       <c r="A46" s="4"/>
       <c r="B46" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
@@ -8687,13 +8703,13 @@
     <row r="47" ht="28.8" spans="1:7">
       <c r="A47" s="4"/>
       <c r="B47" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
@@ -8702,13 +8718,13 @@
     <row r="48" ht="28.8" spans="1:7">
       <c r="A48" s="4"/>
       <c r="B48" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>370</v>
+        <v>301</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>369</v>
+        <v>300</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>15</v>
@@ -8719,13 +8735,13 @@
     <row r="49" ht="28.8" spans="1:7">
       <c r="A49" s="4"/>
       <c r="B49" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
@@ -8734,13 +8750,13 @@
     <row r="50" ht="28.8" spans="1:7">
       <c r="A50" s="4"/>
       <c r="B50" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>372</v>
+        <v>305</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>371</v>
+        <v>304</v>
       </c>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
@@ -8749,13 +8765,13 @@
     <row r="51" ht="28.8" spans="1:7">
       <c r="A51" s="4"/>
       <c r="B51" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>374</v>
+        <v>307</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>373</v>
+        <v>306</v>
       </c>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
@@ -8764,13 +8780,13 @@
     <row r="52" ht="28.8" spans="1:7">
       <c r="A52" s="4"/>
       <c r="B52" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>376</v>
+        <v>309</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>375</v>
+        <v>308</v>
       </c>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
@@ -8779,13 +8795,13 @@
     <row r="53" ht="28.8" spans="1:7">
       <c r="A53" s="4"/>
       <c r="B53" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>378</v>
+        <v>311</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>377</v>
+        <v>310</v>
       </c>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
@@ -8794,13 +8810,13 @@
     <row r="54" ht="28.8" spans="1:7">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>380</v>
+        <v>313</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>379</v>
+        <v>312</v>
       </c>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
@@ -8809,13 +8825,13 @@
     <row r="55" ht="28.8" spans="1:7">
       <c r="A55" s="4"/>
       <c r="B55" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>382</v>
+        <v>315</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>381</v>
+        <v>314</v>
       </c>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
@@ -8824,64 +8840,64 @@
     <row r="56" ht="43.2" spans="1:7">
       <c r="A56" s="4"/>
       <c r="B56" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
       <c r="G56" s="4" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="57" ht="28.8" spans="1:7">
       <c r="A57" s="4"/>
       <c r="B57" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
       <c r="G57" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="58" ht="28.8" spans="1:7">
       <c r="A58" s="4"/>
       <c r="B58" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
       <c r="G58" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="59" ht="28.8" spans="1:7">
       <c r="A59" s="4"/>
       <c r="B59" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
@@ -8890,13 +8906,13 @@
     <row r="60" ht="28.8" spans="1:7">
       <c r="A60" s="4"/>
       <c r="B60" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
@@ -8905,30 +8921,30 @@
     <row r="61" ht="72" spans="1:7">
       <c r="A61" s="4"/>
       <c r="B61" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>368</v>
+        <v>299</v>
       </c>
       <c r="E61" s="4"/>
       <c r="F61" s="4" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G61" s="4"/>
     </row>
     <row r="62" ht="28.8" spans="1:7">
       <c r="A62" s="4"/>
       <c r="B62" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
@@ -8937,13 +8953,13 @@
     <row r="63" ht="28.8" spans="1:7">
       <c r="A63" s="4"/>
       <c r="B63" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E63" s="4"/>
       <c r="F63" s="4"/>
@@ -8952,13 +8968,13 @@
     <row r="64" ht="28.8" spans="1:7">
       <c r="A64" s="4"/>
       <c r="B64" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
@@ -8967,13 +8983,13 @@
     <row r="65" ht="28.8" spans="1:7">
       <c r="A65" s="4"/>
       <c r="B65" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="D65" s="4" t="s">
         <v>475</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>474</v>
       </c>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
@@ -8982,13 +8998,13 @@
     <row r="66" ht="28.8" spans="1:7">
       <c r="A66" s="4"/>
       <c r="B66" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>15</v>
@@ -8999,47 +9015,47 @@
     <row r="67" ht="72" spans="1:7">
       <c r="A67" s="4"/>
       <c r="B67" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E67" s="4"/>
       <c r="F67" s="4" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G67" s="4"/>
     </row>
     <row r="68" ht="115.2" spans="1:7">
       <c r="A68" s="4"/>
       <c r="B68" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E68" s="4"/>
       <c r="F68" s="4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G68" s="4"/>
     </row>
     <row r="69" ht="28.8" spans="1:7">
       <c r="A69" s="4"/>
       <c r="B69" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>15</v>
@@ -9050,34 +9066,34 @@
     <row r="70" ht="72" spans="1:7">
       <c r="A70" s="4"/>
       <c r="B70" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>369</v>
+        <v>300</v>
       </c>
       <c r="E70" s="4"/>
       <c r="F70" s="4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G70" s="4"/>
     </row>
     <row r="71" ht="115.2" spans="1:7">
       <c r="A71" s="4"/>
       <c r="B71" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E71" s="4"/>
       <c r="F71" s="4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G71" s="4"/>
     </row>
@@ -9112,13 +9128,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>6</v>
@@ -9129,16 +9145,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>15</v>
@@ -9148,182 +9164,182 @@
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2"/>
       <c r="B4" s="3"/>
       <c r="C4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2"/>
       <c r="B5" s="3"/>
       <c r="C5" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D5" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2"/>
       <c r="B6" s="3"/>
       <c r="C6" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D6" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2"/>
       <c r="B7" s="3"/>
       <c r="C7" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D7" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D8" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D9" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D10" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
       <c r="C11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
       <c r="C12" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2"/>
       <c r="B13" s="3"/>
       <c r="C13" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2"/>
       <c r="B14" s="3"/>
       <c r="C14" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2"/>
       <c r="B15" s="3"/>
       <c r="C15" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2"/>
       <c r="B19" s="3"/>
       <c r="C19" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2"/>
       <c r="B20" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C20" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D20" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>15</v>
@@ -9333,245 +9349,245 @@
       <c r="A21" s="2"/>
       <c r="B21" s="3"/>
       <c r="C21" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D21" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2"/>
       <c r="B22" s="3"/>
       <c r="C22" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D22" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2"/>
       <c r="B23" s="3"/>
       <c r="C23" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D23" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2"/>
       <c r="B24" s="3"/>
       <c r="C24" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D24" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2"/>
       <c r="B25" s="3"/>
       <c r="C25" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D25" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2"/>
       <c r="B26" s="3"/>
       <c r="C26" t="s">
-        <v>386</v>
+        <v>319</v>
       </c>
       <c r="D26" t="s">
-        <v>385</v>
+        <v>318</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2"/>
       <c r="B27" s="3"/>
       <c r="C27" t="s">
-        <v>388</v>
+        <v>321</v>
       </c>
       <c r="D27" t="s">
-        <v>387</v>
+        <v>320</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2"/>
       <c r="B28" s="3"/>
       <c r="C28" t="s">
-        <v>390</v>
+        <v>323</v>
       </c>
       <c r="D28" t="s">
-        <v>389</v>
+        <v>322</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2"/>
       <c r="B29" s="3"/>
       <c r="C29" t="s">
-        <v>392</v>
+        <v>325</v>
       </c>
       <c r="D29" t="s">
-        <v>391</v>
+        <v>324</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2"/>
       <c r="B30" s="3"/>
       <c r="C30" t="s">
-        <v>394</v>
+        <v>327</v>
       </c>
       <c r="D30" t="s">
-        <v>393</v>
+        <v>326</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2"/>
       <c r="B31" s="3"/>
       <c r="C31" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D31" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2"/>
       <c r="B32" s="3"/>
       <c r="C32" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D32" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2"/>
       <c r="B33" s="3"/>
       <c r="C33" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D33" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2"/>
       <c r="B34" s="3"/>
       <c r="C34" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D34" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2"/>
       <c r="B35" s="3"/>
       <c r="C35" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D35" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2"/>
       <c r="B36" s="3"/>
       <c r="C36" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D36" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
       <c r="C37" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D37" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
       <c r="C38" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D38" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2"/>
       <c r="B39" s="3"/>
       <c r="C39" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D39" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2"/>
       <c r="B40" s="3"/>
       <c r="C40" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D40" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2"/>
       <c r="B41" s="3"/>
       <c r="C41" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D41" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2"/>
       <c r="B42" s="3"/>
       <c r="C42" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D42" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2"/>
       <c r="B43" s="3"/>
       <c r="C43" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D43" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="44" ht="19.25" customHeight="1" spans="1:6">
       <c r="A44" s="2"/>
       <c r="B44" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>15</v>
@@ -9581,205 +9597,205 @@
       <c r="A45" s="2"/>
       <c r="B45" s="3"/>
       <c r="C45" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D45" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2"/>
       <c r="B46" s="3"/>
       <c r="C46" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D46" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2"/>
       <c r="B47" s="3"/>
       <c r="C47" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D47" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2"/>
       <c r="B48" s="3"/>
       <c r="C48" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D48" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2"/>
       <c r="B49" s="3"/>
       <c r="C49" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2"/>
       <c r="B50" s="3"/>
       <c r="C50" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2"/>
       <c r="B51" s="3"/>
       <c r="C51" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D51" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2"/>
       <c r="B52" s="3"/>
       <c r="C52" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D52" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2"/>
       <c r="B53" s="3"/>
       <c r="C53" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D53" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2"/>
       <c r="B54" s="3"/>
       <c r="C54" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D54" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2"/>
       <c r="B55" s="3"/>
       <c r="C55" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D55" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2"/>
       <c r="B56" s="3"/>
       <c r="C56" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D56" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2"/>
       <c r="B57" s="3"/>
       <c r="C57" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D57" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2"/>
       <c r="B58" s="3"/>
       <c r="C58" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D58" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2"/>
       <c r="B59" s="3"/>
       <c r="C59" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D59" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2"/>
       <c r="B60" s="3"/>
       <c r="C60" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D60" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2"/>
       <c r="B61" s="3"/>
       <c r="C61" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D61" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2"/>
       <c r="B62" s="3"/>
       <c r="C62" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D62" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2"/>
       <c r="B63" s="3"/>
       <c r="C63" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D63" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2"/>
       <c r="B64" s="3" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C64" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D64" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>15</v>
@@ -9789,192 +9805,192 @@
       <c r="A65" s="2"/>
       <c r="B65" s="3"/>
       <c r="C65" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D65" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2"/>
       <c r="B66" s="3"/>
       <c r="C66" t="s">
-        <v>283</v>
+        <v>332</v>
       </c>
       <c r="D66" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2"/>
       <c r="B67" s="3"/>
       <c r="C67" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D67" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2"/>
       <c r="B68" s="3"/>
       <c r="C68" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D68" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2"/>
       <c r="B69" s="3"/>
       <c r="C69" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D69" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2"/>
       <c r="B70" s="3"/>
       <c r="C70" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D70" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2"/>
       <c r="B71" s="3"/>
       <c r="C71" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D71" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2"/>
       <c r="B72" s="3"/>
       <c r="C72" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D72" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2"/>
       <c r="B73" s="3"/>
       <c r="C73" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D73" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2"/>
       <c r="B74" s="3"/>
       <c r="C74" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D74" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2"/>
       <c r="B75" s="3"/>
       <c r="C75" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D75" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2"/>
       <c r="B76" s="3"/>
       <c r="C76" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D76" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2"/>
       <c r="B77" s="3"/>
       <c r="C77" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D77" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2"/>
       <c r="B78" s="3"/>
       <c r="C78" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D78" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2"/>
       <c r="B79" s="3"/>
       <c r="C79" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D79" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2"/>
       <c r="B80" s="3"/>
       <c r="C80" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D80" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2"/>
       <c r="B81" s="3"/>
       <c r="C81" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D81" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2"/>
       <c r="B82" s="3"/>
       <c r="C82" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D82" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2"/>
       <c r="B83" s="3" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D83" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>15</v>
@@ -9984,180 +10000,180 @@
       <c r="A84" s="2"/>
       <c r="B84" s="3"/>
       <c r="C84" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2"/>
       <c r="B85" s="3"/>
       <c r="C85" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2"/>
       <c r="B86" s="3"/>
       <c r="C86" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2"/>
       <c r="B87" s="3"/>
       <c r="C87" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2"/>
       <c r="B88" s="3"/>
       <c r="C88" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2"/>
       <c r="B89" s="3"/>
       <c r="C89" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D89" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2"/>
       <c r="B90" s="3"/>
       <c r="C90" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D90" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2"/>
       <c r="B91" s="3"/>
       <c r="C91" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D91" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2"/>
       <c r="B92" s="3"/>
       <c r="C92" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D92" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2"/>
       <c r="B93" s="3"/>
       <c r="C93" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D93" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2"/>
       <c r="B94" s="3"/>
       <c r="C94" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D94" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2"/>
       <c r="B95" s="3"/>
       <c r="C95" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D95" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2"/>
       <c r="B96" s="3"/>
       <c r="C96" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D96" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2"/>
       <c r="B97" s="3"/>
       <c r="C97" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D97" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2"/>
       <c r="B98" s="3"/>
       <c r="C98" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D98" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2"/>
       <c r="B99" s="3"/>
       <c r="C99" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D99" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2"/>
       <c r="B100" s="3"/>
       <c r="C100" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D100" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2"/>
       <c r="B101" s="3"/>
       <c r="C101" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D101" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>

--- a/亿纬锂能DA梳理.xlsx
+++ b/亿纬锂能DA梳理.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="报价助手" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1872" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1835" uniqueCount="554">
   <si>
     <t>业务对象</t>
   </si>
@@ -97,9 +97,6 @@
     <t>枚举</t>
   </si>
   <si>
-    <t>简易询盘、询盘、投标、合同</t>
-  </si>
-  <si>
     <t>org_code</t>
   </si>
   <si>
@@ -151,9 +148,6 @@
     <t>客户等级</t>
   </si>
   <si>
-    <t>S、A、B、C</t>
-  </si>
-  <si>
     <t>project_name</t>
   </si>
   <si>
@@ -190,9 +184,6 @@
     <t>税率</t>
   </si>
   <si>
-    <t>13%、6%、3%</t>
-  </si>
-  <si>
     <t>overseas_tax_rate</t>
   </si>
   <si>
@@ -247,9 +238,6 @@
     <t>质量专控要求</t>
   </si>
   <si>
-    <t>无/2502SDM1、2502SDM2C、SDM2F-WK</t>
-  </si>
-  <si>
     <t>is_carbon_footprint</t>
   </si>
   <si>
@@ -355,48 +343,18 @@
     <t>物流测算区域</t>
   </si>
   <si>
-    <t>国际/国内</t>
-  </si>
-  <si>
     <t>trade_term</t>
   </si>
   <si>
     <t>贸易术语</t>
   </si>
   <si>
-    <r>
-      <t>国内：送货上门/客户自提；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>国际：FOB(装运港船上交货)/DDP(完税后交货)/EXW(工厂交货)......</t>
-    </r>
-  </si>
-  <si>
     <t>transport_type</t>
   </si>
   <si>
     <t>运输类型</t>
   </si>
   <si>
-    <t>点对点/按距离</t>
-  </si>
-  <si>
     <t>logistics_fee_adjust</t>
   </si>
   <si>
@@ -634,36 +592,24 @@
     <t>产品技术参数id</t>
   </si>
   <si>
-    <t>锂亚电池F0041W-LF,ER14250/W15,MOLEX5264反，陆运</t>
-  </si>
-  <si>
     <t>machine_model</t>
   </si>
   <si>
     <t>机械号</t>
   </si>
   <si>
-    <t>F0041W-LF</t>
-  </si>
-  <si>
     <t>plug_wire_model</t>
   </si>
   <si>
     <t>插头线型号</t>
   </si>
   <si>
-    <t>5264-2P</t>
-  </si>
-  <si>
     <t>plug_direction</t>
   </si>
   <si>
     <t>插头方向</t>
   </si>
   <si>
-    <t>反向/正向</t>
-  </si>
-  <si>
     <t>wire_length</t>
   </si>
   <si>
@@ -676,9 +622,6 @@
     <t>是否绕线</t>
   </si>
   <si>
-    <t>否</t>
-  </si>
-  <si>
     <t>cell_code</t>
   </si>
   <si>
@@ -691,18 +634,12 @@
     <t>电芯型号</t>
   </si>
   <si>
-    <t>ER14250V1.3</t>
-  </si>
-  <si>
     <t>reference_size</t>
   </si>
   <si>
     <t>参考尺寸</t>
   </si>
   <si>
-    <t>1/2AA</t>
-  </si>
-  <si>
     <t>rated_voltage</t>
   </si>
   <si>
@@ -733,18 +670,12 @@
     <t>工作温度</t>
   </si>
   <si>
-    <t>-55-+85℃</t>
-  </si>
-  <si>
     <t>max_dimension</t>
   </si>
   <si>
     <t>最大尺寸(mm)</t>
   </si>
   <si>
-    <t>14.5x25.4</t>
-  </si>
-  <si>
     <t>weight</t>
   </si>
   <si>
@@ -757,18 +688,12 @@
     <t>存储温度</t>
   </si>
   <si>
-    <t>+30℃</t>
-  </si>
-  <si>
     <t>application_scope</t>
   </si>
   <si>
     <t>应用范围</t>
   </si>
   <si>
-    <t>公共仪表、警报\安全设备、记忆备份、追踪设备、汽车电子、专业电子、实时时钟、等</t>
-  </si>
-  <si>
     <t>component_product_code</t>
   </si>
   <si>
@@ -781,45 +706,30 @@
     <t>电量</t>
   </si>
   <si>
-    <t>140kWh/280kWh</t>
-  </si>
-  <si>
     <t>cooling_type</t>
   </si>
   <si>
     <t>冷却方式</t>
   </si>
   <si>
-    <t>风冷/液冷</t>
-  </si>
-  <si>
     <t>extra_function</t>
   </si>
   <si>
     <t>附加功能</t>
   </si>
   <si>
-    <t>低温加热/云端通讯</t>
-  </si>
-  <si>
     <t>frame_size</t>
   </si>
   <si>
     <t>边框尺寸</t>
   </si>
   <si>
-    <t>30mm、40mm</t>
-  </si>
-  <si>
     <t>frame_color</t>
   </si>
   <si>
     <t>边框颜色</t>
   </si>
   <si>
-    <t>白框 /灰框/黑框</t>
-  </si>
-  <si>
     <t>frame_material</t>
   </si>
   <si>
@@ -844,36 +754,24 @@
     <t>边框膜厚</t>
   </si>
   <si>
-    <t>AA10/AA12</t>
-  </si>
-  <si>
     <t>film_scheme</t>
   </si>
   <si>
     <t>胶膜方案</t>
   </si>
   <si>
-    <t>POE+EVA /双POE</t>
-  </si>
-  <si>
     <t>film_weight</t>
   </si>
   <si>
     <t>胶膜克重</t>
   </si>
   <si>
-    <t>双ECA（400+380）</t>
-  </si>
-  <si>
     <t>connector</t>
   </si>
   <si>
     <t>连接端子</t>
   </si>
   <si>
-    <t>PV-LR5</t>
-  </si>
-  <si>
     <t>avg_cable_length</t>
   </si>
   <si>
@@ -901,27 +799,18 @@
     <t>标签</t>
   </si>
   <si>
-    <t>防震标签/RFID标签/隆基标准</t>
-  </si>
-  <si>
     <t>dust_plug</t>
   </si>
   <si>
     <t>防尘塞</t>
   </si>
   <si>
-    <t>无/防尘塞</t>
-  </si>
-  <si>
     <t>current_bin</t>
   </si>
   <si>
     <t>电流分档</t>
   </si>
   <si>
-    <t>中间档位按0.1A分档/中间档位按0.15A分档/中间档位按0.2A分档</t>
-  </si>
-  <si>
     <t>yield_loss</t>
   </si>
   <si>
@@ -940,9 +829,6 @@
     <t>运输保障方案</t>
   </si>
   <si>
-    <t>加厚包装/标准运输</t>
-  </si>
-  <si>
     <t>other_nonstd_markup</t>
   </si>
   <si>
@@ -967,9 +853,6 @@
     <t>阶段名称</t>
   </si>
   <si>
-    <t>预付款/备料款/发货款/到货款/验收款/质保金</t>
-  </si>
-  <si>
     <t>fund_occupy_days</t>
   </si>
   <si>
@@ -1012,18 +895,12 @@
     <t>物流计算类型</t>
   </si>
   <si>
-    <t>优选/指定</t>
-  </si>
-  <si>
     <t>logistics_type</t>
   </si>
   <si>
     <t>物流类型</t>
   </si>
   <si>
-    <t>快递运输/陆运运输/铁运运输/水运运输</t>
-  </si>
-  <si>
     <t>vehicle_type</t>
   </si>
   <si>
@@ -1042,9 +919,6 @@
     <t>柜型</t>
   </si>
   <si>
-    <t>20GP/40HQ</t>
-  </si>
-  <si>
     <t>clm_calc_bom_head</t>
   </si>
   <si>
@@ -1102,9 +976,6 @@
     <t>ref_bom_header_id</t>
   </si>
   <si>
-    <t>关联clm_calc_bom_head.bom_header_id</t>
-  </si>
-  <si>
     <t>bom_line_id</t>
   </si>
   <si>
@@ -1199,9 +1070,6 @@
   </si>
   <si>
     <t>枚举值</t>
-  </si>
-  <si>
-    <t>定价/报价</t>
   </si>
   <si>
     <t>markup_item_name</t>
@@ -3319,9 +3187,7 @@
       </c>
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
-      <c r="I4" s="9" t="s">
-        <v>21</v>
-      </c>
+      <c r="I4" s="9"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="9" t="s">
@@ -3334,13 +3200,13 @@
         <v>11</v>
       </c>
       <c r="D5" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="F5" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>24</v>
       </c>
       <c r="G5" s="12"/>
       <c r="H5" s="12"/>
@@ -3357,13 +3223,13 @@
         <v>11</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="F6" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>27</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
@@ -3380,13 +3246,13 @@
         <v>11</v>
       </c>
       <c r="D7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="F7" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>30</v>
       </c>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
@@ -3403,10 +3269,10 @@
         <v>11</v>
       </c>
       <c r="D8" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>31</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>32</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>14</v>
@@ -3426,10 +3292,10 @@
         <v>11</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>34</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>14</v>
@@ -3449,13 +3315,13 @@
         <v>11</v>
       </c>
       <c r="D10" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>36</v>
-      </c>
       <c r="F10" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
@@ -3472,19 +3338,17 @@
         <v>11</v>
       </c>
       <c r="D11" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>37</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>38</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G11" s="12"/>
       <c r="H11" s="12"/>
-      <c r="I11" s="2" t="s">
-        <v>39</v>
-      </c>
+      <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="9" t="s">
@@ -3497,10 +3361,10 @@
         <v>11</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>14</v>
@@ -3520,13 +3384,13 @@
         <v>11</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>44</v>
       </c>
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
@@ -3543,13 +3407,13 @@
         <v>11</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
@@ -3566,13 +3430,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="11" t="s">
         <v>47</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>49</v>
       </c>
       <c r="G15" s="12"/>
       <c r="H15" s="12"/>
@@ -3589,19 +3453,17 @@
         <v>11</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G16" s="12"/>
       <c r="H16" s="12"/>
-      <c r="I16" s="14" t="s">
-        <v>52</v>
-      </c>
+      <c r="I16" s="14"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="9" t="s">
@@ -3614,13 +3476,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G17" s="12"/>
       <c r="H17" s="12"/>
@@ -3637,13 +3499,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G18" s="12"/>
       <c r="H18" s="12"/>
@@ -3660,13 +3522,13 @@
         <v>11</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G19" s="12"/>
       <c r="H19" s="12"/>
@@ -3683,13 +3545,13 @@
         <v>11</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G20" s="12"/>
       <c r="H20" s="12"/>
@@ -3706,13 +3568,13 @@
         <v>11</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G21" s="12"/>
       <c r="H21" s="12"/>
@@ -3729,13 +3591,13 @@
         <v>11</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -3752,13 +3614,13 @@
         <v>11</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G23" s="12"/>
       <c r="H23" s="12"/>
@@ -3775,19 +3637,17 @@
         <v>11</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F24" s="10" t="s">
         <v>20</v>
       </c>
       <c r="G24" s="13"/>
       <c r="H24" s="13"/>
-      <c r="I24" s="9" t="s">
-        <v>71</v>
-      </c>
+      <c r="I24" s="9"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="9" t="s">
@@ -3800,13 +3660,13 @@
         <v>11</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="12"/>
@@ -3823,13 +3683,13 @@
         <v>11</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G26" s="12"/>
       <c r="H26" s="12"/>
@@ -3846,13 +3706,13 @@
         <v>11</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G27" s="12"/>
       <c r="H27" s="12"/>
@@ -3869,13 +3729,13 @@
         <v>11</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G28" s="12"/>
       <c r="H28" s="12"/>
@@ -3892,13 +3752,13 @@
         <v>11</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
@@ -3915,13 +3775,13 @@
         <v>11</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
@@ -3938,13 +3798,13 @@
         <v>11</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
@@ -3961,13 +3821,13 @@
         <v>11</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G32" s="12"/>
       <c r="H32" s="12"/>
@@ -3984,13 +3844,13 @@
         <v>11</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
@@ -4007,13 +3867,13 @@
         <v>11</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G34" s="12"/>
       <c r="H34" s="12"/>
@@ -4030,13 +3890,13 @@
         <v>11</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
@@ -4053,13 +3913,13 @@
         <v>11</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G36" s="12"/>
       <c r="H36" s="12"/>
@@ -4076,13 +3936,13 @@
         <v>11</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G37" s="12"/>
       <c r="H37" s="12"/>
@@ -4099,13 +3959,13 @@
         <v>11</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G38" s="12"/>
       <c r="H38" s="12"/>
@@ -4122,13 +3982,13 @@
         <v>11</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F39" s="15" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G39" s="12"/>
       <c r="H39" s="12"/>
@@ -4145,13 +4005,13 @@
         <v>11</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G40" s="12"/>
       <c r="H40" s="12"/>
@@ -4168,19 +4028,17 @@
         <v>11</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F41" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G41" s="12"/>
       <c r="H41" s="12"/>
-      <c r="I41" s="9" t="s">
-        <v>107</v>
-      </c>
+      <c r="I41" s="9"/>
     </row>
     <row r="42" ht="13.5" customHeight="1" spans="1:9">
       <c r="A42" s="9" t="s">
@@ -4193,19 +4051,17 @@
         <v>11</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F42" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G42" s="12"/>
       <c r="H42" s="12"/>
-      <c r="I42" s="16" t="s">
-        <v>110</v>
-      </c>
+      <c r="I42" s="16"/>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="9" t="s">
@@ -4218,19 +4074,17 @@
         <v>11</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F43" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G43" s="12"/>
       <c r="H43" s="12"/>
-      <c r="I43" s="9" t="s">
-        <v>113</v>
-      </c>
+      <c r="I43" s="9"/>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="9" t="s">
@@ -4243,13 +4097,13 @@
         <v>11</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G44" s="12"/>
       <c r="H44" s="12"/>
@@ -4266,13 +4120,13 @@
         <v>11</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G45" s="12"/>
       <c r="H45" s="12"/>
@@ -4289,10 +4143,10 @@
         <v>11</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="F46" s="11" t="s">
         <v>20</v>
@@ -4312,10 +4166,10 @@
         <v>11</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F47" s="11" t="s">
         <v>20</v>
@@ -4329,10 +4183,10 @@
         <v>9</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>12</v>
@@ -4354,16 +4208,16 @@
         <v>9</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F49" s="11" t="s">
         <v>14</v>
@@ -4379,16 +4233,16 @@
         <v>9</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F50" s="11" t="s">
         <v>20</v>
@@ -4402,16 +4256,16 @@
         <v>9</v>
       </c>
       <c r="B51" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E51" s="10" t="s">
         <v>122</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="E51" s="10" t="s">
-        <v>129</v>
       </c>
       <c r="F51" s="11" t="s">
         <v>20</v>
@@ -4425,19 +4279,19 @@
         <v>9</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C52" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D52" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="D52" s="9" t="s">
-        <v>130</v>
-      </c>
       <c r="E52" s="10" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G52" s="12"/>
       <c r="H52" s="12"/>
@@ -4448,16 +4302,16 @@
         <v>9</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="F53" s="11" t="s">
         <v>14</v>
@@ -4471,16 +4325,16 @@
         <v>9</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="F54" s="11" t="s">
         <v>20</v>
@@ -4494,16 +4348,16 @@
         <v>9</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="F55" s="11" t="s">
         <v>14</v>
@@ -4517,16 +4371,16 @@
         <v>9</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="F56" s="11" t="s">
         <v>14</v>
@@ -4540,16 +4394,16 @@
         <v>9</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="F57" s="11" t="s">
         <v>14</v>
@@ -4563,16 +4417,16 @@
         <v>9</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F58" s="11" t="s">
         <v>14</v>
@@ -4586,16 +4440,16 @@
         <v>9</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="F59" s="11" t="s">
         <v>14</v>
@@ -4609,16 +4463,16 @@
         <v>9</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="F60" s="11" t="s">
         <v>14</v>
@@ -4632,16 +4486,16 @@
         <v>9</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F61" s="11" t="s">
         <v>14</v>
@@ -4655,16 +4509,16 @@
         <v>9</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F62" s="11" t="s">
         <v>20</v>
@@ -4678,19 +4532,19 @@
         <v>9</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G63" s="12"/>
       <c r="H63" s="12"/>
@@ -4701,10 +4555,10 @@
         <v>9</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D64" s="9" t="s">
         <v>12</v>
@@ -4726,16 +4580,16 @@
         <v>9</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="F65" s="11" t="s">
         <v>14</v>
@@ -4751,16 +4605,16 @@
         <v>9</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F66" s="11" t="s">
         <v>14</v>
@@ -4774,19 +4628,19 @@
         <v>9</v>
       </c>
       <c r="B67" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E67" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C67" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="D67" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="E67" s="10" t="s">
-        <v>160</v>
-      </c>
       <c r="F67" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G67" s="12"/>
       <c r="H67" s="12"/>
@@ -4797,19 +4651,19 @@
         <v>9</v>
       </c>
       <c r="B68" s="17" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C68" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="D68" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="D68" s="17" t="s">
-        <v>161</v>
-      </c>
       <c r="E68" s="18" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="F68" s="19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G68" s="12"/>
       <c r="H68" s="12"/>
@@ -4820,16 +4674,16 @@
         <v>9</v>
       </c>
       <c r="B69" s="17" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C69" s="17" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D69" s="17" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E69" s="18" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F69" s="19" t="s">
         <v>14</v>
@@ -4843,19 +4697,19 @@
         <v>9</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G70" s="12"/>
       <c r="H70" s="12"/>
@@ -4866,16 +4720,16 @@
         <v>9</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="F71" s="11" t="s">
         <v>14</v>
@@ -4889,16 +4743,16 @@
         <v>9</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="F72" s="11" t="s">
         <v>14</v>
@@ -4912,19 +4766,19 @@
         <v>9</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G73" s="12"/>
       <c r="H73" s="12"/>
@@ -4935,19 +4789,19 @@
         <v>9</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="E74" s="18" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="F74" s="19" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G74" s="12"/>
       <c r="H74" s="12"/>
@@ -4958,19 +4812,19 @@
         <v>9</v>
       </c>
       <c r="B75" s="17" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C75" s="17" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D75" s="17" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="F75" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G75" s="12"/>
       <c r="H75" s="12"/>
@@ -4981,19 +4835,19 @@
         <v>9</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G76" s="12"/>
       <c r="H76" s="12"/>
@@ -5004,19 +4858,19 @@
         <v>9</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G77" s="12"/>
       <c r="H77" s="12"/>
@@ -5027,19 +4881,19 @@
         <v>9</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G78" s="12"/>
       <c r="H78" s="12"/>
@@ -5050,19 +4904,19 @@
         <v>9</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G79" s="12"/>
       <c r="H79" s="12"/>
@@ -5073,19 +4927,19 @@
         <v>9</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G80" s="12"/>
       <c r="H80" s="12"/>
@@ -5096,16 +4950,16 @@
         <v>9</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F81" s="15" t="s">
         <v>20</v>
@@ -5119,10 +4973,10 @@
         <v>9</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D82" s="9" t="s">
         <v>12</v>
@@ -5144,16 +4998,16 @@
         <v>9</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="F83" s="11" t="s">
         <v>14</v>
@@ -5169,16 +5023,16 @@
         <v>9</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="F84" s="11" t="s">
         <v>14</v>
@@ -5194,16 +5048,16 @@
         <v>9</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F85" s="11" t="s">
         <v>20</v>
@@ -5217,16 +5071,16 @@
         <v>9</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F86" s="11" t="s">
         <v>14</v>
@@ -5240,491 +5094,453 @@
         <v>9</v>
       </c>
       <c r="B87" s="17" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C87" s="17" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D87" s="17" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E87" s="18" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="F87" s="19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G87" s="12"/>
       <c r="H87" s="12"/>
-      <c r="I87" s="15">
-        <v>91008277</v>
-      </c>
+      <c r="I87" s="15"/>
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B88" s="17" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C88" s="17" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D88" s="17" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E88" s="18" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F88" s="19" t="s">
         <v>14</v>
       </c>
       <c r="G88" s="12"/>
       <c r="H88" s="12"/>
-      <c r="I88" s="15" t="s">
-        <v>193</v>
-      </c>
+      <c r="I88" s="15"/>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B89" s="17" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C89" s="17" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D89" s="17" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="E89" s="21" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="F89" s="19" t="s">
         <v>14</v>
       </c>
       <c r="G89" s="12"/>
       <c r="H89" s="12"/>
-      <c r="I89" s="15" t="s">
-        <v>196</v>
-      </c>
+      <c r="I89" s="15"/>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B90" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="C90" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="D90" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="E90" s="21" t="s">
         <v>189</v>
-      </c>
-      <c r="C90" s="17" t="s">
-        <v>190</v>
-      </c>
-      <c r="D90" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="E90" s="21" t="s">
-        <v>198</v>
       </c>
       <c r="F90" s="19" t="s">
         <v>14</v>
       </c>
       <c r="G90" s="12"/>
       <c r="H90" s="12"/>
-      <c r="I90" s="15" t="s">
-        <v>199</v>
-      </c>
+      <c r="I90" s="15"/>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B91" s="17" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C91" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="D91" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="D91" s="17" t="s">
-        <v>200</v>
-      </c>
       <c r="E91" s="21" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="F91" s="19" t="s">
         <v>20</v>
       </c>
       <c r="G91" s="12"/>
       <c r="H91" s="12"/>
-      <c r="I91" s="15" t="s">
-        <v>202</v>
-      </c>
+      <c r="I91" s="15"/>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B92" s="17" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C92" s="17" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D92" s="17" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="E92" s="21" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="F92" s="19" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G92" s="12"/>
       <c r="H92" s="12"/>
-      <c r="I92" s="15">
-        <v>16</v>
-      </c>
+      <c r="I92" s="15"/>
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B93" s="17" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C93" s="17" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D93" s="17" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="E93" s="21" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="F93" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G93" s="12"/>
       <c r="H93" s="12"/>
-      <c r="I93" s="15" t="s">
-        <v>207</v>
-      </c>
+      <c r="I93" s="15"/>
     </row>
     <row r="94" spans="1:9">
       <c r="A94" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B94" s="17" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C94" s="17" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D94" s="17" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="E94" s="21" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="F94" s="19" t="s">
         <v>14</v>
       </c>
       <c r="G94" s="12"/>
       <c r="H94" s="12"/>
-      <c r="I94" s="15">
-        <v>81005049</v>
-      </c>
+      <c r="I94" s="15"/>
     </row>
     <row r="95" spans="1:9">
       <c r="A95" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B95" s="17" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C95" s="17" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D95" s="17" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="E95" s="21" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="F95" s="19" t="s">
         <v>14</v>
       </c>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
-      <c r="I95" s="15" t="s">
-        <v>212</v>
-      </c>
+      <c r="I95" s="15"/>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C96" s="17" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D96" s="17" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="E96" s="21" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="F96" s="19" t="s">
         <v>14</v>
       </c>
       <c r="G96" s="12"/>
       <c r="H96" s="12"/>
-      <c r="I96" s="15" t="s">
-        <v>215</v>
-      </c>
+      <c r="I96" s="15"/>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B97" s="17" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C97" s="17" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D97" s="17" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="E97" s="21" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="F97" s="19" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G97" s="12"/>
       <c r="H97" s="12"/>
-      <c r="I97" s="15">
-        <v>3.6</v>
-      </c>
+      <c r="I97" s="15"/>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B98" s="17" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C98" s="17" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D98" s="17" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="E98" s="21" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="F98" s="19" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G98" s="12"/>
       <c r="H98" s="12"/>
-      <c r="I98" s="15">
-        <v>1200</v>
-      </c>
+      <c r="I98" s="15"/>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B99" s="17" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C99" s="17" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D99" s="17" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="E99" s="21" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="F99" s="19" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G99" s="12"/>
       <c r="H99" s="12"/>
-      <c r="I99" s="15">
-        <v>35</v>
-      </c>
+      <c r="I99" s="15"/>
     </row>
     <row r="100" spans="1:9">
       <c r="A100" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B100" s="17" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C100" s="17" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D100" s="17" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="E100" s="21" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="F100" s="19" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G100" s="12"/>
       <c r="H100" s="12"/>
-      <c r="I100" s="15">
-        <v>50</v>
-      </c>
+      <c r="I100" s="15"/>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B101" s="17" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C101" s="17" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D101" s="17" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="E101" s="21" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F101" s="19" t="s">
         <v>14</v>
       </c>
       <c r="G101" s="12"/>
       <c r="H101" s="12"/>
-      <c r="I101" s="15" t="s">
-        <v>226</v>
-      </c>
+      <c r="I101" s="15"/>
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B102" s="17" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C102" s="17" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D102" s="17" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="E102" s="21" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="F102" s="19" t="s">
         <v>14</v>
       </c>
       <c r="G102" s="12"/>
       <c r="H102" s="12"/>
-      <c r="I102" s="15" t="s">
-        <v>229</v>
-      </c>
+      <c r="I102" s="15"/>
     </row>
     <row r="103" spans="1:9">
       <c r="A103" s="22" t="s">
         <v>9</v>
       </c>
       <c r="B103" s="22" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C103" s="22" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D103" s="22" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="E103" s="23" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="F103" s="24" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G103" s="25"/>
       <c r="H103" s="25"/>
-      <c r="I103" s="26">
-        <v>10</v>
-      </c>
+      <c r="I103" s="26"/>
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B104" s="17" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C104" s="17" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D104" s="17" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="E104" s="21" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="F104" s="19" t="s">
         <v>14</v>
       </c>
       <c r="G104" s="12"/>
       <c r="H104" s="12"/>
-      <c r="I104" s="15" t="s">
-        <v>234</v>
-      </c>
+      <c r="I104" s="15"/>
     </row>
     <row r="105" spans="1:9">
       <c r="A105" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B105" s="17" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C105" s="17" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D105" s="17" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="E105" s="21" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="F105" s="19" t="s">
         <v>14</v>
       </c>
       <c r="G105" s="12"/>
       <c r="H105" s="12"/>
-      <c r="I105" s="15" t="s">
-        <v>237</v>
-      </c>
+      <c r="I105" s="15"/>
     </row>
     <row r="106" spans="1:9">
       <c r="A106" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E106" s="10" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="F106" s="11" t="s">
         <v>14</v>
@@ -5738,16 +5554,16 @@
         <v>9</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="F107" s="11" t="s">
         <v>14</v>
@@ -5761,16 +5577,16 @@
         <v>9</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="E108" s="10" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="F108" s="11" t="s">
         <v>14</v>
@@ -5784,141 +5600,131 @@
         <v>9</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="F109" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G109" s="12"/>
       <c r="H109" s="12"/>
-      <c r="I109" s="9" t="s">
-        <v>242</v>
-      </c>
+      <c r="I109" s="9"/>
     </row>
     <row r="110" spans="1:9">
       <c r="A110" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="F110" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G110" s="12"/>
       <c r="H110" s="12"/>
-      <c r="I110" s="9" t="s">
-        <v>245</v>
-      </c>
+      <c r="I110" s="9"/>
     </row>
     <row r="111" spans="1:9">
       <c r="A111" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="F111" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G111" s="12"/>
       <c r="H111" s="12"/>
-      <c r="I111" s="9" t="s">
-        <v>248</v>
-      </c>
+      <c r="I111" s="9"/>
     </row>
     <row r="112" spans="1:9">
       <c r="A112" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>249</v>
+        <v>228</v>
       </c>
       <c r="E112" s="10" t="s">
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="F112" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G112" s="12"/>
       <c r="H112" s="12"/>
-      <c r="I112" s="9" t="s">
-        <v>251</v>
-      </c>
+      <c r="I112" s="9"/>
     </row>
     <row r="113" spans="1:9">
       <c r="A113" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="F113" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G113" s="12"/>
       <c r="H113" s="12"/>
-      <c r="I113" s="9" t="s">
-        <v>254</v>
-      </c>
+      <c r="I113" s="9"/>
     </row>
     <row r="114" spans="1:9">
       <c r="A114" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="E114" s="10" t="s">
-        <v>256</v>
+        <v>233</v>
       </c>
       <c r="F114" s="11" t="s">
         <v>20</v>
@@ -5932,16 +5738,16 @@
         <v>9</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="F115" s="11" t="s">
         <v>20</v>
@@ -5955,16 +5761,16 @@
         <v>9</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="E116" s="10" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
       <c r="F116" s="11" t="s">
         <v>20</v>
@@ -5978,116 +5784,108 @@
         <v>9</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="F117" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G117" s="12"/>
       <c r="H117" s="12"/>
-      <c r="I117" s="9" t="s">
-        <v>263</v>
-      </c>
+      <c r="I117" s="9"/>
     </row>
     <row r="118" spans="1:9">
       <c r="A118" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="E118" s="10" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
       <c r="F118" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G118" s="12"/>
       <c r="H118" s="12"/>
-      <c r="I118" s="9" t="s">
-        <v>266</v>
-      </c>
+      <c r="I118" s="9"/>
     </row>
     <row r="119" spans="1:9">
       <c r="A119" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>267</v>
+        <v>242</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>268</v>
+        <v>243</v>
       </c>
       <c r="F119" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G119" s="12"/>
       <c r="H119" s="12"/>
-      <c r="I119" s="9" t="s">
-        <v>269</v>
-      </c>
+      <c r="I119" s="9"/>
     </row>
     <row r="120" spans="1:9">
       <c r="A120" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="E120" s="10" t="s">
-        <v>271</v>
+        <v>245</v>
       </c>
       <c r="F120" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G120" s="12"/>
       <c r="H120" s="12"/>
-      <c r="I120" s="9" t="s">
-        <v>272</v>
-      </c>
+      <c r="I120" s="9"/>
     </row>
     <row r="121" spans="1:9">
       <c r="A121" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>273</v>
+        <v>246</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>274</v>
+        <v>247</v>
       </c>
       <c r="F121" s="11" t="s">
         <v>20</v>
@@ -6101,19 +5899,19 @@
         <v>9</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>275</v>
+        <v>248</v>
       </c>
       <c r="E122" s="10" t="s">
-        <v>276</v>
+        <v>249</v>
       </c>
       <c r="F122" s="11" t="s">
-        <v>277</v>
+        <v>250</v>
       </c>
       <c r="G122" s="12"/>
       <c r="H122" s="12"/>
@@ -6124,19 +5922,19 @@
         <v>9</v>
       </c>
       <c r="B123" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="F123" s="11" t="s">
-        <v>277</v>
+        <v>250</v>
       </c>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
@@ -6147,91 +5945,85 @@
         <v>9</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E124" s="10" t="s">
-        <v>281</v>
+        <v>254</v>
       </c>
       <c r="F124" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G124" s="12"/>
       <c r="H124" s="12"/>
-      <c r="I124" s="9" t="s">
-        <v>282</v>
-      </c>
+      <c r="I124" s="9"/>
     </row>
     <row r="125" spans="1:9">
       <c r="A125" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B125" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>283</v>
+        <v>255</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>284</v>
+        <v>256</v>
       </c>
       <c r="F125" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G125" s="12"/>
       <c r="H125" s="12"/>
-      <c r="I125" s="9" t="s">
-        <v>285</v>
-      </c>
+      <c r="I125" s="9"/>
     </row>
     <row r="126" spans="1:9">
       <c r="A126" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="E126" s="10" t="s">
-        <v>287</v>
+        <v>258</v>
       </c>
       <c r="F126" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G126" s="12"/>
       <c r="H126" s="12"/>
-      <c r="I126" s="9" t="s">
-        <v>288</v>
-      </c>
+      <c r="I126" s="9"/>
     </row>
     <row r="127" spans="1:9">
       <c r="A127" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B127" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>289</v>
+        <v>259</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="F127" s="11" t="s">
         <v>20</v>
@@ -6245,19 +6037,19 @@
         <v>9</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>291</v>
+        <v>261</v>
       </c>
       <c r="E128" s="10" t="s">
-        <v>292</v>
+        <v>262</v>
       </c>
       <c r="F128" s="11" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G128" s="12"/>
       <c r="H128" s="12"/>
@@ -6268,44 +6060,42 @@
         <v>9</v>
       </c>
       <c r="B129" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C129" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>293</v>
+        <v>263</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>294</v>
+        <v>264</v>
       </c>
       <c r="F129" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G129" s="12"/>
       <c r="H129" s="12"/>
-      <c r="I129" s="9" t="s">
-        <v>295</v>
-      </c>
+      <c r="I129" s="9"/>
     </row>
     <row r="130" spans="1:9">
       <c r="A130" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B130" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C130" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>296</v>
+        <v>265</v>
       </c>
       <c r="E130" s="10" t="s">
-        <v>297</v>
+        <v>266</v>
       </c>
       <c r="F130" s="11" t="s">
-        <v>277</v>
+        <v>250</v>
       </c>
       <c r="G130" s="12"/>
       <c r="H130" s="12"/>
@@ -6316,10 +6106,10 @@
         <v>9</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c r="C131" s="9" t="s">
-        <v>299</v>
+        <v>268</v>
       </c>
       <c r="D131" s="9" t="s">
         <v>12</v>
@@ -6341,16 +6131,16 @@
         <v>9</v>
       </c>
       <c r="B132" s="9" t="s">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c r="C132" s="9" t="s">
-        <v>299</v>
+        <v>268</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>300</v>
+        <v>269</v>
       </c>
       <c r="E132" s="10" t="s">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="F132" s="11" t="s">
         <v>14</v>
@@ -6366,41 +6156,39 @@
         <v>9</v>
       </c>
       <c r="B133" s="9" t="s">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>299</v>
+        <v>268</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>302</v>
+        <v>271</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>303</v>
+        <v>272</v>
       </c>
       <c r="F133" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G133" s="12"/>
       <c r="H133" s="12"/>
-      <c r="I133" s="9" t="s">
-        <v>304</v>
-      </c>
+      <c r="I133" s="9"/>
     </row>
     <row r="134" spans="1:9">
       <c r="A134" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B134" s="9" t="s">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c r="C134" s="9" t="s">
-        <v>299</v>
+        <v>268</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>305</v>
+        <v>273</v>
       </c>
       <c r="E134" s="10" t="s">
-        <v>306</v>
+        <v>274</v>
       </c>
       <c r="F134" s="11" t="s">
         <v>20</v>
@@ -6414,19 +6202,19 @@
         <v>9</v>
       </c>
       <c r="B135" s="9" t="s">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c r="C135" s="9" t="s">
-        <v>299</v>
+        <v>268</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>307</v>
+        <v>275</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>308</v>
+        <v>276</v>
       </c>
       <c r="F135" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G135" s="12"/>
       <c r="H135" s="12"/>
@@ -6437,19 +6225,19 @@
         <v>9</v>
       </c>
       <c r="B136" s="9" t="s">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>299</v>
+        <v>268</v>
       </c>
       <c r="D136" s="9" t="s">
-        <v>309</v>
+        <v>277</v>
       </c>
       <c r="E136" s="10" t="s">
-        <v>310</v>
+        <v>278</v>
       </c>
       <c r="F136" s="11" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G136" s="12"/>
       <c r="H136" s="12"/>
@@ -6460,16 +6248,16 @@
         <v>9</v>
       </c>
       <c r="B137" s="9" t="s">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>299</v>
+        <v>268</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>311</v>
+        <v>279</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>312</v>
+        <v>280</v>
       </c>
       <c r="F137" s="11" t="s">
         <v>20</v>
@@ -6483,10 +6271,10 @@
         <v>9</v>
       </c>
       <c r="B138" s="9" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="C138" s="9" t="s">
-        <v>314</v>
+        <v>282</v>
       </c>
       <c r="D138" s="9" t="s">
         <v>12</v>
@@ -6508,16 +6296,16 @@
         <v>9</v>
       </c>
       <c r="B139" s="9" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="C139" s="9" t="s">
-        <v>314</v>
+        <v>282</v>
       </c>
       <c r="D139" s="9" t="s">
-        <v>315</v>
+        <v>283</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>316</v>
+        <v>284</v>
       </c>
       <c r="F139" s="11" t="s">
         <v>14</v>
@@ -6533,66 +6321,62 @@
         <v>9</v>
       </c>
       <c r="B140" s="9" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="C140" s="9" t="s">
-        <v>314</v>
+        <v>282</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>317</v>
+        <v>285</v>
       </c>
       <c r="E140" s="10" t="s">
-        <v>318</v>
+        <v>286</v>
       </c>
       <c r="F140" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G140" s="12"/>
       <c r="H140" s="12"/>
-      <c r="I140" s="9" t="s">
-        <v>319</v>
-      </c>
+      <c r="I140" s="9"/>
     </row>
     <row r="141" spans="1:9">
       <c r="A141" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B141" s="9" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="C141" s="9" t="s">
-        <v>314</v>
+        <v>282</v>
       </c>
       <c r="D141" s="9" t="s">
-        <v>320</v>
+        <v>287</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>321</v>
+        <v>288</v>
       </c>
       <c r="F141" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G141" s="12"/>
       <c r="H141" s="12"/>
-      <c r="I141" s="9" t="s">
-        <v>322</v>
-      </c>
+      <c r="I141" s="9"/>
     </row>
     <row r="142" spans="1:9">
       <c r="A142" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B142" s="9" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>314</v>
+        <v>282</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>323</v>
+        <v>289</v>
       </c>
       <c r="E142" s="10" t="s">
-        <v>324</v>
+        <v>290</v>
       </c>
       <c r="F142" s="11" t="s">
         <v>20</v>
@@ -6606,16 +6390,16 @@
         <v>9</v>
       </c>
       <c r="B143" s="9" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="C143" s="9" t="s">
-        <v>314</v>
+        <v>282</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>325</v>
+        <v>291</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>326</v>
+        <v>292</v>
       </c>
       <c r="F143" s="11" t="s">
         <v>20</v>
@@ -6629,35 +6413,33 @@
         <v>9</v>
       </c>
       <c r="B144" s="9" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>314</v>
+        <v>282</v>
       </c>
       <c r="D144" s="9" t="s">
-        <v>327</v>
+        <v>293</v>
       </c>
       <c r="E144" s="10" t="s">
-        <v>328</v>
+        <v>294</v>
       </c>
       <c r="F144" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G144" s="12"/>
       <c r="H144" s="12"/>
-      <c r="I144" s="9" t="s">
-        <v>329</v>
-      </c>
+      <c r="I144" s="9"/>
     </row>
     <row r="145" spans="1:9">
       <c r="A145" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>330</v>
+        <v>295</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="D145" s="3" t="s">
         <v>12</v>
@@ -6679,16 +6461,16 @@
         <v>9</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>330</v>
+        <v>295</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E146" s="10" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="F146" s="11" t="s">
         <v>14</v>
@@ -6704,16 +6486,16 @@
         <v>9</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>330</v>
+        <v>295</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>332</v>
+        <v>297</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>333</v>
+        <v>298</v>
       </c>
       <c r="F147" s="11" t="s">
         <v>14</v>
@@ -6729,16 +6511,16 @@
         <v>9</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>330</v>
+        <v>295</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>334</v>
+        <v>299</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>335</v>
+        <v>300</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>14</v>
@@ -6752,16 +6534,16 @@
         <v>9</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>330</v>
+        <v>295</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>336</v>
+        <v>301</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>337</v>
+        <v>302</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>14</v>
@@ -6775,16 +6557,16 @@
         <v>9</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>330</v>
+        <v>295</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>338</v>
+        <v>303</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>14</v>
@@ -6798,16 +6580,16 @@
         <v>9</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>330</v>
+        <v>295</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>339</v>
+        <v>304</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>14</v>
@@ -6821,16 +6603,16 @@
         <v>9</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>330</v>
+        <v>295</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>340</v>
+        <v>305</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>341</v>
+        <v>306</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>14</v>
@@ -6844,19 +6626,19 @@
         <v>9</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>330</v>
+        <v>295</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>342</v>
+        <v>307</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>343</v>
+        <v>308</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G153" s="3"/>
       <c r="H153" s="20"/>
@@ -6867,16 +6649,16 @@
         <v>9</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>330</v>
+        <v>295</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>345</v>
+        <v>310</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>14</v>
@@ -6890,16 +6672,16 @@
         <v>9</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>346</v>
+        <v>311</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>347</v>
+        <v>312</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>348</v>
+        <v>313</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>333</v>
+        <v>298</v>
       </c>
       <c r="F155" s="11" t="s">
         <v>14</v>
@@ -6908,25 +6690,23 @@
       <c r="H155" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="I155" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="I155" s="2"/>
     </row>
     <row r="156" spans="1:9">
       <c r="A156" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>346</v>
+        <v>311</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>347</v>
+        <v>312</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>350</v>
+        <v>314</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>351</v>
+        <v>315</v>
       </c>
       <c r="F156" s="11" t="s">
         <v>14</v>
@@ -6942,19 +6722,19 @@
         <v>9</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>346</v>
+        <v>311</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>347</v>
+        <v>312</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>352</v>
+        <v>316</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>353</v>
+        <v>317</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G157" s="3"/>
       <c r="H157" s="20"/>
@@ -6965,16 +6745,16 @@
         <v>9</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>346</v>
+        <v>311</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>347</v>
+        <v>312</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>354</v>
+        <v>318</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>355</v>
+        <v>319</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>14</v>
@@ -6988,16 +6768,16 @@
         <v>9</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>346</v>
+        <v>311</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>347</v>
+        <v>312</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>356</v>
+        <v>320</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>357</v>
+        <v>321</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>14</v>
@@ -7011,16 +6791,16 @@
         <v>9</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>346</v>
+        <v>311</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>347</v>
+        <v>312</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>358</v>
+        <v>322</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>359</v>
+        <v>323</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>14</v>
@@ -7034,16 +6814,16 @@
         <v>9</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>346</v>
+        <v>311</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>347</v>
+        <v>312</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>360</v>
+        <v>324</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>361</v>
+        <v>325</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>14</v>
@@ -7057,19 +6837,19 @@
         <v>9</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>346</v>
+        <v>311</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>347</v>
+        <v>312</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>362</v>
+        <v>326</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>363</v>
+        <v>327</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G162" s="3"/>
       <c r="H162" s="20"/>
@@ -7080,16 +6860,16 @@
         <v>9</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>346</v>
+        <v>311</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>347</v>
+        <v>312</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>364</v>
+        <v>328</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>365</v>
+        <v>329</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>14</v>
@@ -7103,19 +6883,19 @@
         <v>9</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>346</v>
+        <v>311</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>347</v>
+        <v>312</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>366</v>
+        <v>330</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>367</v>
+        <v>331</v>
       </c>
       <c r="F164" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G164" s="3"/>
       <c r="H164" s="20"/>
@@ -7126,19 +6906,19 @@
         <v>9</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>346</v>
+        <v>311</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>347</v>
+        <v>312</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>368</v>
+        <v>332</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>369</v>
+        <v>333</v>
       </c>
       <c r="F165" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G165" s="20"/>
       <c r="H165" s="20"/>
@@ -7149,19 +6929,19 @@
         <v>9</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>346</v>
+        <v>311</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>347</v>
+        <v>312</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>370</v>
+        <v>334</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>371</v>
+        <v>335</v>
       </c>
       <c r="F166" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G166" s="20"/>
       <c r="H166" s="20"/>
@@ -7172,19 +6952,19 @@
         <v>9</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>346</v>
+        <v>311</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>347</v>
+        <v>312</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>372</v>
+        <v>336</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>373</v>
+        <v>337</v>
       </c>
       <c r="F167" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G167" s="20"/>
       <c r="H167" s="20"/>
@@ -7195,19 +6975,19 @@
         <v>9</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>346</v>
+        <v>311</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>347</v>
+        <v>312</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>374</v>
+        <v>338</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>375</v>
+        <v>339</v>
       </c>
       <c r="F168" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G168" s="20"/>
       <c r="H168" s="20"/>
@@ -7218,10 +6998,10 @@
         <v>9</v>
       </c>
       <c r="B169" s="9" t="s">
-        <v>376</v>
+        <v>340</v>
       </c>
       <c r="C169" s="9" t="s">
-        <v>377</v>
+        <v>341</v>
       </c>
       <c r="D169" s="9" t="s">
         <v>12</v>
@@ -7243,16 +7023,16 @@
         <v>9</v>
       </c>
       <c r="B170" s="9" t="s">
-        <v>376</v>
+        <v>340</v>
       </c>
       <c r="C170" s="9" t="s">
-        <v>377</v>
+        <v>341</v>
       </c>
       <c r="D170" s="9" t="s">
-        <v>378</v>
+        <v>342</v>
       </c>
       <c r="E170" s="10" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="F170" s="11" t="s">
         <v>14</v>
@@ -7270,44 +7050,42 @@
         <v>9</v>
       </c>
       <c r="B171" s="9" t="s">
-        <v>376</v>
+        <v>340</v>
       </c>
       <c r="C171" s="9" t="s">
-        <v>377</v>
+        <v>341</v>
       </c>
       <c r="D171" s="9" t="s">
-        <v>379</v>
+        <v>343</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>380</v>
+        <v>344</v>
       </c>
       <c r="F171" s="11" t="s">
-        <v>381</v>
+        <v>345</v>
       </c>
       <c r="G171" s="12"/>
       <c r="H171" s="12"/>
-      <c r="I171" s="2" t="s">
-        <v>382</v>
-      </c>
+      <c r="I171" s="2"/>
     </row>
     <row r="172" spans="1:9">
       <c r="A172" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B172" s="9" t="s">
-        <v>376</v>
+        <v>340</v>
       </c>
       <c r="C172" s="9" t="s">
-        <v>377</v>
+        <v>341</v>
       </c>
       <c r="D172" s="9" t="s">
-        <v>352</v>
+        <v>316</v>
       </c>
       <c r="E172" s="10" t="s">
-        <v>353</v>
+        <v>317</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G172" s="12"/>
       <c r="H172" s="12"/>
@@ -7318,16 +7096,16 @@
         <v>9</v>
       </c>
       <c r="B173" s="9" t="s">
-        <v>376</v>
+        <v>340</v>
       </c>
       <c r="C173" s="9" t="s">
-        <v>377</v>
+        <v>341</v>
       </c>
       <c r="D173" s="9" t="s">
-        <v>383</v>
+        <v>346</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>384</v>
+        <v>347</v>
       </c>
       <c r="F173" s="11" t="s">
         <v>14</v>
@@ -7341,16 +7119,16 @@
         <v>9</v>
       </c>
       <c r="B174" s="9" t="s">
-        <v>376</v>
+        <v>340</v>
       </c>
       <c r="C174" s="9" t="s">
-        <v>377</v>
+        <v>341</v>
       </c>
       <c r="D174" s="9" t="s">
-        <v>385</v>
+        <v>348</v>
       </c>
       <c r="E174" s="10" t="s">
-        <v>386</v>
+        <v>349</v>
       </c>
       <c r="F174" s="11" t="s">
         <v>14</v>
@@ -7361,19 +7139,19 @@
     </row>
     <row r="175" spans="1:9">
       <c r="A175" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B175" s="9" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="C175" s="9" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="D175" s="9" t="s">
-        <v>390</v>
+        <v>353</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>391</v>
+        <v>354</v>
       </c>
       <c r="F175" s="11" t="s">
         <v>14</v>
@@ -7386,19 +7164,19 @@
     </row>
     <row r="176" spans="1:9">
       <c r="A176" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B176" s="9" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="C176" s="9" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="D176" s="9" t="s">
-        <v>392</v>
+        <v>355</v>
       </c>
       <c r="E176" s="10" t="s">
-        <v>393</v>
+        <v>356</v>
       </c>
       <c r="F176" s="11" t="s">
         <v>14</v>
@@ -7409,19 +7187,19 @@
     </row>
     <row r="177" spans="1:9">
       <c r="A177" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B177" s="9" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="C177" s="9" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="D177" s="9" t="s">
-        <v>394</v>
+        <v>357</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>395</v>
+        <v>358</v>
       </c>
       <c r="F177" s="11" t="s">
         <v>14</v>
@@ -7432,13 +7210,13 @@
     </row>
     <row r="178" spans="1:9">
       <c r="A178" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B178" s="9" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="C178" s="9" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="D178" s="9" t="s">
         <v>12</v>
@@ -7457,19 +7235,19 @@
     </row>
     <row r="179" spans="1:9">
       <c r="A179" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B179" s="9" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="C179" s="9" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="D179" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>396</v>
+        <v>359</v>
       </c>
       <c r="F179" s="11" t="s">
         <v>14</v>
@@ -7480,22 +7258,22 @@
     </row>
     <row r="180" spans="1:9">
       <c r="A180" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B180" s="9" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="C180" s="9" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="D180" s="9" t="s">
-        <v>397</v>
+        <v>360</v>
       </c>
       <c r="E180" s="10" t="s">
-        <v>398</v>
+        <v>361</v>
       </c>
       <c r="F180" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G180" s="12"/>
       <c r="H180" s="12"/>
@@ -7503,19 +7281,19 @@
     </row>
     <row r="181" spans="1:9">
       <c r="A181" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B181" s="9" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="C181" s="9" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="D181" s="9" t="s">
-        <v>399</v>
+        <v>362</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>400</v>
+        <v>363</v>
       </c>
       <c r="F181" s="11" t="s">
         <v>20</v>
@@ -7526,19 +7304,19 @@
     </row>
     <row r="182" spans="1:9">
       <c r="A182" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B182" s="9" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="C182" s="9" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="D182" s="9" t="s">
-        <v>401</v>
+        <v>364</v>
       </c>
       <c r="E182" s="10" t="s">
-        <v>402</v>
+        <v>365</v>
       </c>
       <c r="F182" s="11" t="s">
         <v>20</v>
@@ -7549,22 +7327,22 @@
     </row>
     <row r="183" spans="1:9">
       <c r="A183" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B183" s="9" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="C183" s="9" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="D183" s="9" t="s">
-        <v>403</v>
+        <v>366</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>404</v>
+        <v>367</v>
       </c>
       <c r="F183" s="11" t="s">
-        <v>405</v>
+        <v>368</v>
       </c>
       <c r="G183" s="12"/>
       <c r="H183" s="12"/>
@@ -7572,22 +7350,22 @@
     </row>
     <row r="184" spans="1:9">
       <c r="A184" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B184" s="9" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="C184" s="9" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="D184" s="9" t="s">
-        <v>406</v>
+        <v>369</v>
       </c>
       <c r="E184" s="10" t="s">
-        <v>407</v>
+        <v>370</v>
       </c>
       <c r="F184" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G184" s="12"/>
       <c r="H184" s="12"/>
@@ -7595,22 +7373,22 @@
     </row>
     <row r="185" spans="1:9">
       <c r="A185" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B185" s="9" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="C185" s="9" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="D185" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E185" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E185" s="10" t="s">
-        <v>29</v>
-      </c>
       <c r="F185" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G185" s="12"/>
       <c r="H185" s="12"/>
@@ -7618,22 +7396,22 @@
     </row>
     <row r="186" spans="1:9">
       <c r="A186" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B186" s="9" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="C186" s="9" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="D186" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E186" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F186" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G186" s="12"/>
       <c r="H186" s="12"/>
@@ -7641,19 +7419,19 @@
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B187" s="9" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="C187" s="9" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="D187" s="9" t="s">
-        <v>408</v>
+        <v>371</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>409</v>
+        <v>372</v>
       </c>
       <c r="F187" s="11" t="s">
         <v>20</v>
@@ -7664,19 +7442,19 @@
     </row>
     <row r="188" spans="1:9">
       <c r="A188" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B188" s="9" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="C188" s="9" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="D188" s="9" t="s">
-        <v>410</v>
+        <v>373</v>
       </c>
       <c r="E188" s="10" t="s">
-        <v>411</v>
+        <v>374</v>
       </c>
       <c r="F188" s="11" t="s">
         <v>14</v>
@@ -7687,19 +7465,19 @@
     </row>
     <row r="189" spans="1:9">
       <c r="A189" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="C189" s="9" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>412</v>
+        <v>375</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>413</v>
+        <v>376</v>
       </c>
       <c r="F189" s="11" t="s">
         <v>14</v>
@@ -7710,19 +7488,19 @@
     </row>
     <row r="190" spans="1:9">
       <c r="A190" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="C190" s="9" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>414</v>
+        <v>377</v>
       </c>
       <c r="E190" s="10" t="s">
-        <v>415</v>
+        <v>378</v>
       </c>
       <c r="F190" s="11" t="s">
         <v>14</v>
@@ -7733,19 +7511,19 @@
     </row>
     <row r="191" spans="1:9">
       <c r="A191" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="C191" s="9" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>416</v>
+        <v>379</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>417</v>
+        <v>380</v>
       </c>
       <c r="F191" s="11" t="s">
         <v>14</v>
@@ -7756,19 +7534,19 @@
     </row>
     <row r="192" spans="1:9">
       <c r="A192" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="C192" s="9" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>418</v>
+        <v>381</v>
       </c>
       <c r="E192" s="10" t="s">
-        <v>419</v>
+        <v>382</v>
       </c>
       <c r="F192" s="11" t="s">
         <v>14</v>
@@ -7779,19 +7557,19 @@
     </row>
     <row r="193" spans="1:9">
       <c r="A193" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="C193" s="9" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>420</v>
+        <v>383</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>421</v>
+        <v>384</v>
       </c>
       <c r="F193" s="11" t="s">
         <v>14</v>
@@ -7802,22 +7580,22 @@
     </row>
     <row r="194" spans="1:9">
       <c r="A194" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="C194" s="9" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="D194" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E194" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E194" s="10" t="s">
-        <v>36</v>
-      </c>
       <c r="F194" s="11" t="s">
-        <v>422</v>
+        <v>385</v>
       </c>
       <c r="G194" s="12"/>
       <c r="H194" s="12"/>
@@ -7825,22 +7603,22 @@
     </row>
     <row r="195" spans="1:9">
       <c r="A195" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="B195" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="C195" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="D195" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="E195" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="B195" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="C195" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="D195" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="E195" s="10" t="s">
-        <v>424</v>
-      </c>
       <c r="F195" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G195" s="12"/>
       <c r="H195" s="12"/>
@@ -7848,19 +7626,19 @@
     </row>
     <row r="196" spans="1:9">
       <c r="A196" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B196" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="C196" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="D196" s="9" t="s">
         <v>388</v>
       </c>
-      <c r="C196" s="9" t="s">
+      <c r="E196" s="10" t="s">
         <v>389</v>
-      </c>
-      <c r="D196" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="E196" s="10" t="s">
-        <v>426</v>
       </c>
       <c r="F196" s="11" t="s">
         <v>14</v>
@@ -7871,19 +7649,19 @@
     </row>
     <row r="197" spans="1:9">
       <c r="A197" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="C197" s="9" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>427</v>
+        <v>390</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>428</v>
+        <v>391</v>
       </c>
       <c r="F197" s="11" t="s">
         <v>14</v>
@@ -7894,19 +7672,19 @@
     </row>
     <row r="198" spans="1:9">
       <c r="A198" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="C198" s="9" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>429</v>
+        <v>392</v>
       </c>
       <c r="E198" s="10" t="s">
-        <v>430</v>
+        <v>393</v>
       </c>
       <c r="F198" s="11" t="s">
         <v>14</v>
@@ -7917,19 +7695,19 @@
     </row>
     <row r="199" spans="1:9">
       <c r="A199" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="C199" s="9" t="s">
-        <v>432</v>
+        <v>395</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>390</v>
+        <v>353</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>391</v>
+        <v>354</v>
       </c>
       <c r="F199" s="11" t="s">
         <v>14</v>
@@ -7942,19 +7720,19 @@
     </row>
     <row r="200" spans="1:9">
       <c r="A200" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="C200" s="9" t="s">
-        <v>432</v>
+        <v>395</v>
       </c>
       <c r="D200" s="9" t="s">
-        <v>433</v>
+        <v>396</v>
       </c>
       <c r="E200" s="10" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="F200" s="11" t="s">
         <v>14</v>
@@ -7967,22 +7745,22 @@
     </row>
     <row r="201" spans="1:9">
       <c r="A201" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B201" s="9" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="C201" s="9" t="s">
-        <v>432</v>
+        <v>395</v>
       </c>
       <c r="D201" s="9" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F201" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G201" s="12"/>
       <c r="H201" s="12"/>
@@ -7990,22 +7768,22 @@
     </row>
     <row r="202" spans="1:9">
       <c r="A202" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B202" s="9" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="C202" s="9" t="s">
-        <v>432</v>
+        <v>395</v>
       </c>
       <c r="D202" s="9" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="E202" s="10" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F202" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G202" s="12"/>
       <c r="H202" s="12"/>
@@ -8013,22 +7791,22 @@
     </row>
     <row r="203" spans="1:9">
       <c r="A203" s="17" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B203" s="17" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="C203" s="17" t="s">
-        <v>432</v>
+        <v>395</v>
       </c>
       <c r="D203" s="17" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E203" s="18" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="F203" s="19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G203" s="12"/>
       <c r="H203" s="12"/>
@@ -8036,19 +7814,19 @@
     </row>
     <row r="204" spans="1:9">
       <c r="A204" s="17" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B204" s="17" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="C204" s="17" t="s">
-        <v>432</v>
+        <v>395</v>
       </c>
       <c r="D204" s="17" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E204" s="18" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F204" s="19" t="s">
         <v>14</v>
@@ -8059,22 +7837,22 @@
     </row>
     <row r="205" spans="1:9">
       <c r="A205" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B205" s="9" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="C205" s="9" t="s">
-        <v>432</v>
+        <v>395</v>
       </c>
       <c r="D205" s="9" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="F205" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G205" s="12"/>
       <c r="H205" s="12"/>
@@ -8082,19 +7860,19 @@
     </row>
     <row r="206" spans="1:9">
       <c r="A206" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B206" s="9" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="C206" s="9" t="s">
-        <v>432</v>
+        <v>395</v>
       </c>
       <c r="D206" s="9" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E206" s="10" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="F206" s="11" t="s">
         <v>14</v>
@@ -8105,19 +7883,19 @@
     </row>
     <row r="207" spans="1:9">
       <c r="A207" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B207" s="9" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="C207" s="9" t="s">
-        <v>432</v>
+        <v>395</v>
       </c>
       <c r="D207" s="9" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="F207" s="11" t="s">
         <v>14</v>
@@ -8128,22 +7906,22 @@
     </row>
     <row r="208" spans="1:9">
       <c r="A208" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B208" s="9" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="C208" s="9" t="s">
-        <v>432</v>
+        <v>395</v>
       </c>
       <c r="D208" s="9" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="E208" s="10" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="F208" s="11" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G208" s="12"/>
       <c r="H208" s="12"/>
@@ -8151,22 +7929,22 @@
     </row>
     <row r="209" spans="1:9">
       <c r="A209" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B209" s="9" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="C209" s="9" t="s">
-        <v>432</v>
+        <v>395</v>
       </c>
       <c r="D209" s="9" t="s">
-        <v>434</v>
+        <v>397</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>435</v>
+        <v>398</v>
       </c>
       <c r="F209" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G209" s="12"/>
       <c r="H209" s="12"/>
@@ -8174,22 +7952,22 @@
     </row>
     <row r="210" spans="1:9">
       <c r="A210" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B210" s="9" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>432</v>
+        <v>395</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>436</v>
+        <v>399</v>
       </c>
       <c r="E210" s="10" t="s">
-        <v>437</v>
+        <v>400</v>
       </c>
       <c r="F210" s="11" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G210" s="12"/>
       <c r="H210" s="12"/>
@@ -8197,22 +7975,22 @@
     </row>
     <row r="211" spans="1:9">
       <c r="A211" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B211" s="9" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>432</v>
+        <v>395</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>438</v>
+        <v>401</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>439</v>
+        <v>402</v>
       </c>
       <c r="F211" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G211" s="12"/>
       <c r="H211" s="12"/>
@@ -8220,22 +7998,22 @@
     </row>
     <row r="212" spans="1:9">
       <c r="A212" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B212" s="9" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>432</v>
+        <v>395</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>440</v>
+        <v>403</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>441</v>
+        <v>404</v>
       </c>
       <c r="F212" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G212" s="20"/>
       <c r="H212" s="20"/>
@@ -8243,22 +8021,22 @@
     </row>
     <row r="213" spans="1:9">
       <c r="A213" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B213" s="9" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>432</v>
+        <v>395</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F213" s="11" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G213" s="20"/>
       <c r="H213" s="20"/>
@@ -8266,22 +8044,22 @@
     </row>
     <row r="214" spans="1:9">
       <c r="A214" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="B214" s="9" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>432</v>
+        <v>395</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>442</v>
+        <v>405</v>
       </c>
       <c r="E214" s="10" t="s">
-        <v>443</v>
+        <v>406</v>
       </c>
       <c r="F214" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G214" s="12"/>
       <c r="H214" s="12"/>
@@ -8315,13 +8093,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>444</v>
+        <v>407</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>445</v>
+        <v>408</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>5</v>
@@ -8338,16 +8116,16 @@
     </row>
     <row r="2" ht="28.8" customHeight="1" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>446</v>
+        <v>409</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>447</v>
+        <v>410</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>448</v>
+        <v>411</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>449</v>
+        <v>412</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
@@ -8359,13 +8137,13 @@
     <row r="3" ht="28.8" spans="1:8">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
-        <v>447</v>
+        <v>410</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>450</v>
+        <v>413</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>451</v>
+        <v>414</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -8375,13 +8153,13 @@
     <row r="4" ht="28.8" spans="1:8">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
-        <v>447</v>
+        <v>410</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>452</v>
+        <v>415</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>453</v>
+        <v>416</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -8391,13 +8169,13 @@
     <row r="5" ht="28.8" spans="1:8">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>447</v>
+        <v>410</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>341</v>
+        <v>306</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -8407,13 +8185,13 @@
     <row r="6" ht="28.8" spans="1:8">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
-        <v>447</v>
+        <v>410</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>454</v>
+        <v>417</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>455</v>
+        <v>418</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -8423,13 +8201,13 @@
     <row r="7" ht="28.8" spans="1:8">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
-        <v>447</v>
+        <v>410</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>456</v>
+        <v>419</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>457</v>
+        <v>420</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -8439,13 +8217,13 @@
     <row r="8" ht="28.8" spans="1:8">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>447</v>
+        <v>410</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>458</v>
+        <v>421</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>459</v>
+        <v>422</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -8455,13 +8233,13 @@
     <row r="9" ht="28.8" spans="1:8">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>460</v>
+        <v>423</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>461</v>
+        <v>424</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>462</v>
+        <v>425</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
@@ -8473,13 +8251,13 @@
     <row r="10" ht="28.8" spans="1:8">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
-        <v>460</v>
+        <v>423</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>463</v>
+        <v>426</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>464</v>
+        <v>427</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -8489,13 +8267,13 @@
     <row r="11" ht="28.8" spans="1:8">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
-        <v>460</v>
+        <v>423</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>465</v>
+        <v>428</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>466</v>
+        <v>429</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -8505,49 +8283,49 @@
     <row r="12" ht="115.2" spans="1:8">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
-        <v>460</v>
+        <v>423</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>467</v>
+        <v>430</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>468</v>
+        <v>431</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>469</v>
+        <v>432</v>
       </c>
     </row>
     <row r="13" ht="43.2" spans="1:8">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>460</v>
+        <v>423</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>470</v>
+        <v>433</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>472</v>
+        <v>435</v>
       </c>
       <c r="H13" s="3"/>
     </row>
     <row r="14" ht="28.8" spans="1:8">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
-        <v>460</v>
+        <v>423</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>473</v>
+        <v>436</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>474</v>
+        <v>437</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -8557,13 +8335,13 @@
     <row r="15" ht="43.2" spans="1:8">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
-        <v>475</v>
+        <v>438</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>476</v>
+        <v>439</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>476</v>
+        <v>439</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3" t="s">
@@ -8575,49 +8353,49 @@
     <row r="16" ht="43.2" spans="1:8">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
-        <v>475</v>
+        <v>438</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>463</v>
+        <v>426</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>462</v>
+        <v>425</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
-        <v>477</v>
+        <v>440</v>
       </c>
       <c r="H16" s="3"/>
     </row>
     <row r="17" ht="43.2" spans="1:8">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
-        <v>475</v>
+        <v>438</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>478</v>
+        <v>441</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>479</v>
+        <v>442</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>480</v>
+        <v>443</v>
       </c>
       <c r="H17" s="3"/>
     </row>
     <row r="18" ht="43.2" spans="1:8">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
-        <v>475</v>
+        <v>438</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>481</v>
+        <v>444</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>482</v>
+        <v>445</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -8627,13 +8405,13 @@
     <row r="19" ht="43.2" spans="1:8">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
-        <v>475</v>
+        <v>438</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>483</v>
+        <v>446</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>484</v>
+        <v>447</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -8643,13 +8421,13 @@
     <row r="20" ht="28.8" spans="1:8">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
-        <v>485</v>
+        <v>448</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>486</v>
+        <v>449</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>479</v>
+        <v>442</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
@@ -8661,31 +8439,31 @@
     <row r="21" ht="28.8" customHeight="1" spans="1:8">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
-        <v>485</v>
+        <v>448</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>454</v>
+        <v>417</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>455</v>
+        <v>418</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>487</v>
+        <v>450</v>
       </c>
     </row>
     <row r="22" ht="28.8" spans="1:8">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
-        <v>485</v>
+        <v>448</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>488</v>
+        <v>451</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>489</v>
+        <v>452</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
@@ -8695,13 +8473,13 @@
     <row r="23" ht="28.8" spans="1:8">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
-        <v>485</v>
+        <v>448</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>490</v>
+        <v>453</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>491</v>
+        <v>454</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
@@ -8711,13 +8489,13 @@
     <row r="24" ht="28.8" spans="1:8">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
-        <v>485</v>
+        <v>448</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>492</v>
+        <v>455</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>493</v>
+        <v>456</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
@@ -8727,13 +8505,13 @@
     <row r="25" ht="28.8" spans="1:8">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
-        <v>485</v>
+        <v>448</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>494</v>
+        <v>457</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -8743,13 +8521,13 @@
     <row r="26" ht="28.8" spans="1:8">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
-        <v>485</v>
+        <v>448</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>496</v>
+        <v>459</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>497</v>
+        <v>460</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
@@ -8759,13 +8537,13 @@
     <row r="27" ht="28.8" spans="1:8">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
-        <v>485</v>
+        <v>448</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>498</v>
+        <v>461</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>499</v>
+        <v>462</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
@@ -8775,13 +8553,13 @@
     <row r="28" ht="28.8" spans="1:8">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
-        <v>485</v>
+        <v>448</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>500</v>
+        <v>463</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>501</v>
+        <v>464</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -8791,13 +8569,13 @@
     <row r="29" ht="28.8" spans="1:8">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
-        <v>485</v>
+        <v>448</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>502</v>
+        <v>465</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>503</v>
+        <v>466</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
@@ -8807,13 +8585,13 @@
     <row r="30" ht="28.8" spans="1:8">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
-        <v>485</v>
+        <v>448</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>504</v>
+        <v>467</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>505</v>
+        <v>468</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
@@ -8823,13 +8601,13 @@
     <row r="31" ht="28.8" spans="1:8">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
-        <v>485</v>
+        <v>448</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>506</v>
+        <v>469</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>507</v>
+        <v>470</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
@@ -8839,13 +8617,13 @@
     <row r="32" ht="28.8" spans="1:8">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
-        <v>485</v>
+        <v>448</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>508</v>
+        <v>471</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>509</v>
+        <v>472</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
@@ -8855,13 +8633,13 @@
     <row r="33" ht="28.8" spans="1:8">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
-        <v>485</v>
+        <v>448</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>510</v>
+        <v>473</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>511</v>
+        <v>474</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
@@ -8870,16 +8648,16 @@
     </row>
     <row r="34" ht="28.8" customHeight="1" spans="1:8">
       <c r="A34" s="3" t="s">
-        <v>512</v>
+        <v>475</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>513</v>
+        <v>476</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>333</v>
+        <v>298</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>332</v>
+        <v>297</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3" t="s">
@@ -8891,13 +8669,13 @@
     <row r="35" ht="28.8" spans="1:8">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
-        <v>513</v>
+        <v>476</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>335</v>
+        <v>300</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>334</v>
+        <v>299</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -8907,13 +8685,13 @@
     <row r="36" ht="28.8" spans="1:8">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
-        <v>513</v>
+        <v>476</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>337</v>
+        <v>302</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>336</v>
+        <v>301</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -8923,13 +8701,13 @@
     <row r="37" ht="28.8" spans="1:8">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
-        <v>513</v>
+        <v>476</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>338</v>
+        <v>303</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
@@ -8939,13 +8717,13 @@
     <row r="38" ht="28.8" spans="1:8">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
-        <v>513</v>
+        <v>476</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>339</v>
+        <v>304</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -8955,13 +8733,13 @@
     <row r="39" ht="28.8" spans="1:8">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
-        <v>513</v>
+        <v>476</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>341</v>
+        <v>306</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>340</v>
+        <v>305</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -8971,13 +8749,13 @@
     <row r="40" ht="28.8" spans="1:8">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
-        <v>513</v>
+        <v>476</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>343</v>
+        <v>308</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>342</v>
+        <v>307</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
@@ -8987,13 +8765,13 @@
     <row r="41" ht="28.8" spans="1:8">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
-        <v>513</v>
+        <v>476</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>345</v>
+        <v>310</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
@@ -9003,13 +8781,13 @@
     <row r="42" ht="28.8" spans="1:8">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
-        <v>513</v>
+        <v>476</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>473</v>
+        <v>436</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>474</v>
+        <v>437</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -9019,13 +8797,13 @@
     <row r="43" ht="28.8" spans="1:8">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
-        <v>513</v>
+        <v>476</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>514</v>
+        <v>477</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>515</v>
+        <v>478</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
@@ -9035,13 +8813,13 @@
     <row r="44" ht="28.8" spans="1:8">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
-        <v>513</v>
+        <v>476</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>516</v>
+        <v>479</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>517</v>
+        <v>480</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -9051,13 +8829,13 @@
     <row r="45" ht="28.8" spans="1:8">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
-        <v>513</v>
+        <v>476</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>518</v>
+        <v>481</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>503</v>
+        <v>466</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
@@ -9067,13 +8845,13 @@
     <row r="46" ht="28.8" spans="1:8">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
-        <v>513</v>
+        <v>476</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>519</v>
+        <v>482</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>520</v>
+        <v>483</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
@@ -9083,13 +8861,13 @@
     <row r="47" ht="28.8" spans="1:8">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
-        <v>513</v>
+        <v>476</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>521</v>
+        <v>484</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>522</v>
+        <v>485</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
@@ -9099,13 +8877,13 @@
     <row r="48" ht="28.8" spans="1:8">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>351</v>
+        <v>315</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>350</v>
+        <v>314</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
@@ -9117,13 +8895,13 @@
     <row r="49" ht="28.8" spans="1:8">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>353</v>
+        <v>317</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>352</v>
+        <v>316</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
@@ -9133,13 +8911,13 @@
     <row r="50" ht="28.8" spans="1:8">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>355</v>
+        <v>319</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>354</v>
+        <v>318</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
@@ -9149,13 +8927,13 @@
     <row r="51" ht="28.8" spans="1:8">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>357</v>
+        <v>321</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>356</v>
+        <v>320</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
@@ -9165,13 +8943,13 @@
     <row r="52" ht="28.8" spans="1:8">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>359</v>
+        <v>323</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>358</v>
+        <v>322</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
@@ -9181,13 +8959,13 @@
     <row r="53" ht="28.8" spans="1:8">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>361</v>
+        <v>325</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>360</v>
+        <v>324</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
@@ -9197,13 +8975,13 @@
     <row r="54" ht="28.8" spans="1:8">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>363</v>
+        <v>327</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>362</v>
+        <v>326</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
@@ -9213,13 +8991,13 @@
     <row r="55" ht="28.8" spans="1:8">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>365</v>
+        <v>329</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>364</v>
+        <v>328</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
@@ -9229,67 +9007,67 @@
     <row r="56" ht="86.4" spans="1:8">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>524</v>
+        <v>487</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>525</v>
+        <v>488</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
-        <v>526</v>
+        <v>489</v>
       </c>
     </row>
     <row r="57" ht="28.8" spans="1:8">
       <c r="A57" s="3"/>
       <c r="B57" s="3" t="s">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>527</v>
+        <v>490</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>528</v>
+        <v>491</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
-        <v>529</v>
+        <v>492</v>
       </c>
     </row>
     <row r="58" ht="28.8" spans="1:8">
       <c r="A58" s="3"/>
       <c r="B58" s="3" t="s">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>530</v>
+        <v>493</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>531</v>
+        <v>494</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3"/>
       <c r="H58" s="3" t="s">
-        <v>529</v>
+        <v>492</v>
       </c>
     </row>
     <row r="59" ht="28.8" spans="1:8">
       <c r="A59" s="3"/>
       <c r="B59" s="3" t="s">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>532</v>
+        <v>495</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>533</v>
+        <v>496</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
@@ -9299,13 +9077,13 @@
     <row r="60" ht="28.8" spans="1:8">
       <c r="A60" s="3"/>
       <c r="B60" s="3" t="s">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>534</v>
+        <v>497</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>535</v>
+        <v>498</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
@@ -9315,31 +9093,31 @@
     <row r="61" ht="43.2" spans="1:8">
       <c r="A61" s="3"/>
       <c r="B61" s="3" t="s">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>536</v>
+        <v>499</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>348</v>
+        <v>313</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
-        <v>537</v>
+        <v>500</v>
       </c>
       <c r="H61" s="3"/>
     </row>
     <row r="62" ht="28.8" spans="1:8">
       <c r="A62" s="3"/>
       <c r="B62" s="3" t="s">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>516</v>
+        <v>479</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>517</v>
+        <v>480</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
@@ -9349,13 +9127,13 @@
     <row r="63" ht="28.8" spans="1:8">
       <c r="A63" s="3"/>
       <c r="B63" s="3" t="s">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>518</v>
+        <v>481</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>503</v>
+        <v>466</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
@@ -9365,13 +9143,13 @@
     <row r="64" ht="28.8" spans="1:8">
       <c r="A64" s="3"/>
       <c r="B64" s="3" t="s">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>519</v>
+        <v>482</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>520</v>
+        <v>483</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
@@ -9381,13 +9159,13 @@
     <row r="65" ht="28.8" spans="1:8">
       <c r="A65" s="3"/>
       <c r="B65" s="3" t="s">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>521</v>
+        <v>484</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>522</v>
+        <v>485</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
@@ -9397,13 +9175,13 @@
     <row r="66" ht="28.8" spans="1:8">
       <c r="A66" s="3"/>
       <c r="B66" s="3" t="s">
-        <v>538</v>
+        <v>501</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>539</v>
+        <v>502</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>540</v>
+        <v>503</v>
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
@@ -9415,49 +9193,49 @@
     <row r="67" ht="43.2" spans="1:8">
       <c r="A67" s="3"/>
       <c r="B67" s="3" t="s">
-        <v>538</v>
+        <v>501</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>541</v>
+        <v>504</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>542</v>
+        <v>505</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>537</v>
+        <v>500</v>
       </c>
       <c r="H67" s="3"/>
     </row>
     <row r="68" ht="72" spans="1:8">
       <c r="A68" s="3"/>
       <c r="B68" s="3" t="s">
-        <v>538</v>
+        <v>501</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>543</v>
+        <v>506</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>544</v>
+        <v>507</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
-        <v>545</v>
+        <v>508</v>
       </c>
       <c r="H68" s="3"/>
     </row>
     <row r="69" ht="28.8" spans="1:8">
       <c r="A69" s="3"/>
       <c r="B69" s="3" t="s">
-        <v>546</v>
+        <v>509</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>539</v>
+        <v>502</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>540</v>
+        <v>503</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
@@ -9469,49 +9247,49 @@
     <row r="70" ht="43.2" spans="1:8">
       <c r="A70" s="3"/>
       <c r="B70" s="3" t="s">
-        <v>546</v>
+        <v>509</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>547</v>
+        <v>510</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>350</v>
+        <v>314</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>548</v>
+        <v>511</v>
       </c>
       <c r="H70" s="3"/>
     </row>
     <row r="71" ht="72" spans="1:8">
       <c r="A71" s="3"/>
       <c r="B71" s="3" t="s">
-        <v>546</v>
+        <v>509</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>543</v>
+        <v>506</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>544</v>
+        <v>507</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>545</v>
+        <v>508</v>
       </c>
       <c r="H71" s="3"/>
     </row>
     <row r="72" customHeight="1" spans="1:8">
       <c r="A72" s="2"/>
       <c r="B72" s="4" t="s">
-        <v>549</v>
+        <v>512</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>476</v>
+        <v>439</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>476</v>
+        <v>439</v>
       </c>
       <c r="E72" s="5" t="s">
         <v>14</v>
@@ -9526,10 +9304,10 @@
       <c r="A73" s="2"/>
       <c r="B73" s="4"/>
       <c r="C73" s="5" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E73" s="5" t="s">
         <v>14</v>
@@ -9544,10 +9322,10 @@
       <c r="A74" s="2"/>
       <c r="B74" s="4"/>
       <c r="C74" s="5" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E74" s="5" t="s">
         <v>14</v>
@@ -9560,10 +9338,10 @@
       <c r="A75" s="2"/>
       <c r="B75" s="4"/>
       <c r="C75" s="5" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="E75" s="5" t="s">
         <v>14</v>
@@ -9576,10 +9354,10 @@
       <c r="A76" s="2"/>
       <c r="B76" s="4"/>
       <c r="C76" s="5" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="E76" s="5" t="s">
         <v>14</v>
@@ -9592,10 +9370,10 @@
       <c r="A77" s="2"/>
       <c r="B77" s="4"/>
       <c r="C77" s="5" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="E77" s="5" t="s">
         <v>20</v>
@@ -9608,13 +9386,13 @@
       <c r="A78" s="2"/>
       <c r="B78" s="4"/>
       <c r="C78" s="5" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="F78" s="5"/>
       <c r="G78" s="5"/>
@@ -9624,13 +9402,13 @@
       <c r="A79" s="2"/>
       <c r="B79" s="4"/>
       <c r="C79" s="5" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F79" s="5"/>
       <c r="G79" s="2"/>
@@ -9640,10 +9418,10 @@
       <c r="A80" s="2"/>
       <c r="B80" s="4"/>
       <c r="C80" s="5" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="E80" s="5" t="s">
         <v>14</v>
@@ -9656,10 +9434,10 @@
       <c r="A81" s="2"/>
       <c r="B81" s="4"/>
       <c r="C81" s="5" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="E81" s="5" t="s">
         <v>14</v>
@@ -9672,10 +9450,10 @@
       <c r="A82" s="2"/>
       <c r="B82" s="4"/>
       <c r="C82" s="5" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="E82" s="5" t="s">
         <v>14</v>
@@ -9688,13 +9466,13 @@
       <c r="A83" s="2"/>
       <c r="B83" s="4"/>
       <c r="C83" s="5" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="2"/>
@@ -9704,13 +9482,13 @@
       <c r="A84" s="2"/>
       <c r="B84" s="4"/>
       <c r="C84" s="5" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="F84" s="5"/>
       <c r="G84" s="2"/>
@@ -9720,13 +9498,13 @@
       <c r="A85" s="2"/>
       <c r="B85" s="4"/>
       <c r="C85" s="5" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="F85" s="5"/>
       <c r="G85" s="2"/>
@@ -9736,13 +9514,13 @@
       <c r="A86" s="2"/>
       <c r="B86" s="4"/>
       <c r="C86" s="5" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="F86" s="5"/>
       <c r="G86" s="2"/>
@@ -9752,10 +9530,10 @@
       <c r="A87" s="2"/>
       <c r="B87" s="4"/>
       <c r="C87" s="5" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="E87" s="5" t="s">
         <v>14</v>
@@ -9768,10 +9546,10 @@
       <c r="A88" s="2"/>
       <c r="B88" s="4"/>
       <c r="C88" s="5" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="E88" s="5" t="s">
         <v>14</v>
@@ -9784,13 +9562,13 @@
       <c r="A89" s="2"/>
       <c r="B89" s="4"/>
       <c r="C89" s="5" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="F89" s="5"/>
       <c r="G89" s="2"/>
@@ -9800,10 +9578,10 @@
       <c r="A90" s="2"/>
       <c r="B90" s="4"/>
       <c r="C90" s="5" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="E90" s="5" t="s">
         <v>14</v>
@@ -9816,10 +9594,10 @@
       <c r="A91" s="2"/>
       <c r="B91" s="4"/>
       <c r="C91" s="5" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="E91" s="5" t="s">
         <v>14</v>
@@ -9860,13 +9638,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>444</v>
+        <v>407</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>445</v>
+        <v>408</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>6</v>
@@ -9877,16 +9655,16 @@
     </row>
     <row r="2" customHeight="1" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>550</v>
+        <v>513</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>551</v>
+        <v>514</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>486</v>
+        <v>449</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>552</v>
+        <v>515</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>15</v>
@@ -9897,10 +9675,10 @@
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>553</v>
+        <v>516</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>554</v>
+        <v>517</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -9909,10 +9687,10 @@
       <c r="A4" s="2"/>
       <c r="B4" s="3"/>
       <c r="C4" s="2" t="s">
-        <v>494</v>
+        <v>457</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>555</v>
+        <v>518</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -9921,10 +9699,10 @@
       <c r="A5" s="2"/>
       <c r="B5" s="3"/>
       <c r="C5" s="2" t="s">
-        <v>556</v>
+        <v>519</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>557</v>
+        <v>520</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -9933,10 +9711,10 @@
       <c r="A6" s="2"/>
       <c r="B6" s="3"/>
       <c r="C6" s="2" t="s">
-        <v>558</v>
+        <v>521</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>559</v>
+        <v>522</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -9945,10 +9723,10 @@
       <c r="A7" s="2"/>
       <c r="B7" s="3"/>
       <c r="C7" s="2" t="s">
-        <v>496</v>
+        <v>459</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>497</v>
+        <v>460</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -9957,10 +9735,10 @@
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" s="2" t="s">
-        <v>498</v>
+        <v>461</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>499</v>
+        <v>462</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
@@ -9969,10 +9747,10 @@
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="2" t="s">
-        <v>500</v>
+        <v>463</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>501</v>
+        <v>464</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -9981,10 +9759,10 @@
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="2" t="s">
-        <v>502</v>
+        <v>465</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>503</v>
+        <v>466</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -9993,10 +9771,10 @@
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
       <c r="C11" s="2" t="s">
-        <v>504</v>
+        <v>467</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>505</v>
+        <v>468</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -10005,10 +9783,10 @@
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
       <c r="C12" s="2" t="s">
-        <v>506</v>
+        <v>469</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>507</v>
+        <v>470</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -10017,10 +9795,10 @@
       <c r="A13" s="2"/>
       <c r="B13" s="3"/>
       <c r="C13" s="2" t="s">
-        <v>508</v>
+        <v>471</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>509</v>
+        <v>472</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -10029,10 +9807,10 @@
       <c r="A14" s="2"/>
       <c r="B14" s="3"/>
       <c r="C14" s="2" t="s">
-        <v>510</v>
+        <v>473</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>511</v>
+        <v>474</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -10041,10 +9819,10 @@
       <c r="A15" s="2"/>
       <c r="B15" s="3"/>
       <c r="C15" s="2" t="s">
-        <v>560</v>
+        <v>523</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>561</v>
+        <v>524</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -10053,10 +9831,10 @@
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="2" t="s">
-        <v>562</v>
+        <v>525</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>563</v>
+        <v>526</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
@@ -10065,10 +9843,10 @@
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="2" t="s">
-        <v>564</v>
+        <v>527</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>565</v>
+        <v>528</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
@@ -10077,10 +9855,10 @@
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="2" t="s">
-        <v>566</v>
+        <v>529</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>567</v>
+        <v>530</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
@@ -10089,10 +9867,10 @@
       <c r="A19" s="2"/>
       <c r="B19" s="3"/>
       <c r="C19" s="2" t="s">
-        <v>568</v>
+        <v>531</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>569</v>
+        <v>532</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
@@ -10100,13 +9878,13 @@
     <row r="20" customHeight="1" spans="1:6">
       <c r="A20" s="2"/>
       <c r="B20" s="3" t="s">
-        <v>570</v>
+        <v>533</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>486</v>
+        <v>449</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>571</v>
+        <v>534</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>15</v>
@@ -10117,38 +9895,38 @@
       <c r="A21" s="2"/>
       <c r="B21" s="3"/>
       <c r="C21" s="2" t="s">
-        <v>572</v>
+        <v>535</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>449</v>
+        <v>412</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>573</v>
+        <v>536</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2"/>
       <c r="B22" s="3"/>
       <c r="C22" s="2" t="s">
-        <v>452</v>
+        <v>415</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>574</v>
+        <v>537</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
-        <v>575</v>
+        <v>538</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2"/>
       <c r="B23" s="3"/>
       <c r="C23" s="2" t="s">
-        <v>576</v>
+        <v>539</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>577</v>
+        <v>540</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
@@ -10157,10 +9935,10 @@
       <c r="A24" s="2"/>
       <c r="B24" s="3"/>
       <c r="C24" s="2" t="s">
-        <v>532</v>
+        <v>495</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>578</v>
+        <v>541</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
@@ -10169,10 +9947,10 @@
       <c r="A25" s="2"/>
       <c r="B25" s="3"/>
       <c r="C25" s="2" t="s">
-        <v>534</v>
+        <v>497</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>579</v>
+        <v>542</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
@@ -10181,10 +9959,10 @@
       <c r="A26" s="2"/>
       <c r="B26" s="3"/>
       <c r="C26" s="2" t="s">
-        <v>367</v>
+        <v>331</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>366</v>
+        <v>330</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
@@ -10193,10 +9971,10 @@
       <c r="A27" s="2"/>
       <c r="B27" s="3"/>
       <c r="C27" s="2" t="s">
-        <v>369</v>
+        <v>333</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>368</v>
+        <v>332</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
@@ -10205,10 +9983,10 @@
       <c r="A28" s="2"/>
       <c r="B28" s="3"/>
       <c r="C28" s="2" t="s">
-        <v>371</v>
+        <v>335</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>370</v>
+        <v>334</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
@@ -10217,10 +9995,10 @@
       <c r="A29" s="2"/>
       <c r="B29" s="3"/>
       <c r="C29" s="2" t="s">
-        <v>373</v>
+        <v>337</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>372</v>
+        <v>336</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
@@ -10229,10 +10007,10 @@
       <c r="A30" s="2"/>
       <c r="B30" s="3"/>
       <c r="C30" s="2" t="s">
-        <v>375</v>
+        <v>339</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>374</v>
+        <v>338</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
@@ -10241,10 +10019,10 @@
       <c r="A31" s="2"/>
       <c r="B31" s="3"/>
       <c r="C31" s="2" t="s">
-        <v>496</v>
+        <v>459</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>497</v>
+        <v>460</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
@@ -10253,10 +10031,10 @@
       <c r="A32" s="2"/>
       <c r="B32" s="3"/>
       <c r="C32" s="2" t="s">
-        <v>498</v>
+        <v>461</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>499</v>
+        <v>462</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
@@ -10265,10 +10043,10 @@
       <c r="A33" s="2"/>
       <c r="B33" s="3"/>
       <c r="C33" s="2" t="s">
-        <v>500</v>
+        <v>463</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>501</v>
+        <v>464</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -10277,10 +10055,10 @@
       <c r="A34" s="2"/>
       <c r="B34" s="3"/>
       <c r="C34" s="2" t="s">
-        <v>502</v>
+        <v>465</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>503</v>
+        <v>466</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
@@ -10289,10 +10067,10 @@
       <c r="A35" s="2"/>
       <c r="B35" s="3"/>
       <c r="C35" s="2" t="s">
-        <v>504</v>
+        <v>467</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>505</v>
+        <v>468</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
@@ -10301,10 +10079,10 @@
       <c r="A36" s="2"/>
       <c r="B36" s="3"/>
       <c r="C36" s="2" t="s">
-        <v>506</v>
+        <v>469</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>507</v>
+        <v>470</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
@@ -10313,10 +10091,10 @@
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
       <c r="C37" s="2" t="s">
-        <v>508</v>
+        <v>471</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>509</v>
+        <v>472</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
@@ -10325,10 +10103,10 @@
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
       <c r="C38" s="2" t="s">
-        <v>510</v>
+        <v>473</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>511</v>
+        <v>474</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
@@ -10337,10 +10115,10 @@
       <c r="A39" s="2"/>
       <c r="B39" s="3"/>
       <c r="C39" s="2" t="s">
-        <v>560</v>
+        <v>523</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>561</v>
+        <v>524</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
@@ -10349,10 +10127,10 @@
       <c r="A40" s="2"/>
       <c r="B40" s="3"/>
       <c r="C40" s="2" t="s">
-        <v>562</v>
+        <v>525</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>563</v>
+        <v>526</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
@@ -10361,10 +10139,10 @@
       <c r="A41" s="2"/>
       <c r="B41" s="3"/>
       <c r="C41" s="2" t="s">
-        <v>564</v>
+        <v>527</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>565</v>
+        <v>528</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
@@ -10373,10 +10151,10 @@
       <c r="A42" s="2"/>
       <c r="B42" s="3"/>
       <c r="C42" s="2" t="s">
-        <v>566</v>
+        <v>529</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>567</v>
+        <v>530</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
@@ -10385,10 +10163,10 @@
       <c r="A43" s="2"/>
       <c r="B43" s="3"/>
       <c r="C43" s="2" t="s">
-        <v>568</v>
+        <v>531</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>569</v>
+        <v>532</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
@@ -10396,13 +10174,13 @@
     <row r="44" ht="19.25" customHeight="1" spans="1:6">
       <c r="A44" s="2"/>
       <c r="B44" s="3" t="s">
-        <v>580</v>
+        <v>543</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>486</v>
+        <v>449</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>581</v>
+        <v>544</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>15</v>
@@ -10413,10 +10191,10 @@
       <c r="A45" s="2"/>
       <c r="B45" s="3"/>
       <c r="C45" s="2" t="s">
-        <v>582</v>
+        <v>545</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>571</v>
+        <v>534</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
@@ -10425,24 +10203,24 @@
       <c r="A46" s="2"/>
       <c r="B46" s="3"/>
       <c r="C46" s="2" t="s">
-        <v>572</v>
+        <v>535</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>449</v>
+        <v>412</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
-        <v>573</v>
+        <v>536</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2"/>
       <c r="B47" s="3"/>
       <c r="C47" s="2" t="s">
-        <v>452</v>
+        <v>415</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>574</v>
+        <v>537</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
@@ -10451,10 +10229,10 @@
       <c r="A48" s="2"/>
       <c r="B48" s="3"/>
       <c r="C48" s="2" t="s">
-        <v>576</v>
+        <v>539</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>577</v>
+        <v>540</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
@@ -10463,10 +10241,10 @@
       <c r="A49" s="2"/>
       <c r="B49" s="3"/>
       <c r="C49" s="2" t="s">
-        <v>583</v>
+        <v>546</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>584</v>
+        <v>547</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
@@ -10475,10 +10253,10 @@
       <c r="A50" s="2"/>
       <c r="B50" s="3"/>
       <c r="C50" s="2" t="s">
-        <v>585</v>
+        <v>548</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>586</v>
+        <v>549</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
@@ -10487,10 +10265,10 @@
       <c r="A51" s="2"/>
       <c r="B51" s="3"/>
       <c r="C51" s="2" t="s">
-        <v>496</v>
+        <v>459</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>497</v>
+        <v>460</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -10499,10 +10277,10 @@
       <c r="A52" s="2"/>
       <c r="B52" s="3"/>
       <c r="C52" s="2" t="s">
-        <v>498</v>
+        <v>461</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>499</v>
+        <v>462</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
@@ -10511,10 +10289,10 @@
       <c r="A53" s="2"/>
       <c r="B53" s="3"/>
       <c r="C53" s="2" t="s">
-        <v>500</v>
+        <v>463</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>501</v>
+        <v>464</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
@@ -10523,10 +10301,10 @@
       <c r="A54" s="2"/>
       <c r="B54" s="3"/>
       <c r="C54" s="2" t="s">
-        <v>502</v>
+        <v>465</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>503</v>
+        <v>466</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
@@ -10535,10 +10313,10 @@
       <c r="A55" s="2"/>
       <c r="B55" s="3"/>
       <c r="C55" s="2" t="s">
-        <v>504</v>
+        <v>467</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>505</v>
+        <v>468</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
@@ -10547,10 +10325,10 @@
       <c r="A56" s="2"/>
       <c r="B56" s="3"/>
       <c r="C56" s="2" t="s">
-        <v>506</v>
+        <v>469</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>507</v>
+        <v>470</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
@@ -10559,10 +10337,10 @@
       <c r="A57" s="2"/>
       <c r="B57" s="3"/>
       <c r="C57" s="2" t="s">
-        <v>508</v>
+        <v>471</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>509</v>
+        <v>472</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
@@ -10571,10 +10349,10 @@
       <c r="A58" s="2"/>
       <c r="B58" s="3"/>
       <c r="C58" s="2" t="s">
-        <v>510</v>
+        <v>473</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>511</v>
+        <v>474</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
@@ -10583,10 +10361,10 @@
       <c r="A59" s="2"/>
       <c r="B59" s="3"/>
       <c r="C59" s="2" t="s">
-        <v>560</v>
+        <v>523</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>561</v>
+        <v>524</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
@@ -10595,10 +10373,10 @@
       <c r="A60" s="2"/>
       <c r="B60" s="3"/>
       <c r="C60" s="2" t="s">
-        <v>562</v>
+        <v>525</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>563</v>
+        <v>526</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
@@ -10607,10 +10385,10 @@
       <c r="A61" s="2"/>
       <c r="B61" s="3"/>
       <c r="C61" s="2" t="s">
-        <v>564</v>
+        <v>527</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>565</v>
+        <v>528</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
@@ -10619,10 +10397,10 @@
       <c r="A62" s="2"/>
       <c r="B62" s="3"/>
       <c r="C62" s="2" t="s">
-        <v>566</v>
+        <v>529</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>567</v>
+        <v>530</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
@@ -10631,10 +10409,10 @@
       <c r="A63" s="2"/>
       <c r="B63" s="3"/>
       <c r="C63" s="2" t="s">
-        <v>568</v>
+        <v>531</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>569</v>
+        <v>532</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
@@ -10642,13 +10420,13 @@
     <row r="64" customHeight="1" spans="1:6">
       <c r="A64" s="2"/>
       <c r="B64" s="3" t="s">
-        <v>587</v>
+        <v>550</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>486</v>
+        <v>449</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>588</v>
+        <v>551</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>15</v>
@@ -10659,10 +10437,10 @@
       <c r="A65" s="2"/>
       <c r="B65" s="3"/>
       <c r="C65" s="2" t="s">
-        <v>553</v>
+        <v>516</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>554</v>
+        <v>517</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
@@ -10671,10 +10449,10 @@
       <c r="A66" s="2"/>
       <c r="B66" s="3"/>
       <c r="C66" s="2" t="s">
-        <v>380</v>
+        <v>344</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>589</v>
+        <v>552</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
@@ -10683,10 +10461,10 @@
       <c r="A67" s="2"/>
       <c r="B67" s="3"/>
       <c r="C67" s="2" t="s">
-        <v>494</v>
+        <v>457</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>555</v>
+        <v>518</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
@@ -10695,10 +10473,10 @@
       <c r="A68" s="2"/>
       <c r="B68" s="3"/>
       <c r="C68" s="2" t="s">
-        <v>558</v>
+        <v>521</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>559</v>
+        <v>522</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
@@ -10707,10 +10485,10 @@
       <c r="A69" s="2"/>
       <c r="B69" s="3"/>
       <c r="C69" s="2" t="s">
-        <v>556</v>
+        <v>519</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>557</v>
+        <v>520</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
@@ -10719,10 +10497,10 @@
       <c r="A70" s="2"/>
       <c r="B70" s="3"/>
       <c r="C70" s="2" t="s">
-        <v>496</v>
+        <v>459</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>497</v>
+        <v>460</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
@@ -10731,10 +10509,10 @@
       <c r="A71" s="2"/>
       <c r="B71" s="3"/>
       <c r="C71" s="2" t="s">
-        <v>498</v>
+        <v>461</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>499</v>
+        <v>462</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
@@ -10743,10 +10521,10 @@
       <c r="A72" s="2"/>
       <c r="B72" s="3"/>
       <c r="C72" s="2" t="s">
-        <v>500</v>
+        <v>463</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>501</v>
+        <v>464</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
@@ -10755,10 +10533,10 @@
       <c r="A73" s="2"/>
       <c r="B73" s="3"/>
       <c r="C73" s="2" t="s">
-        <v>502</v>
+        <v>465</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>503</v>
+        <v>466</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
@@ -10767,10 +10545,10 @@
       <c r="A74" s="2"/>
       <c r="B74" s="3"/>
       <c r="C74" s="2" t="s">
-        <v>504</v>
+        <v>467</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>505</v>
+        <v>468</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
@@ -10779,10 +10557,10 @@
       <c r="A75" s="2"/>
       <c r="B75" s="3"/>
       <c r="C75" s="2" t="s">
-        <v>506</v>
+        <v>469</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>507</v>
+        <v>470</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
@@ -10791,10 +10569,10 @@
       <c r="A76" s="2"/>
       <c r="B76" s="3"/>
       <c r="C76" s="2" t="s">
-        <v>508</v>
+        <v>471</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>509</v>
+        <v>472</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
@@ -10803,10 +10581,10 @@
       <c r="A77" s="2"/>
       <c r="B77" s="3"/>
       <c r="C77" s="2" t="s">
-        <v>510</v>
+        <v>473</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>511</v>
+        <v>474</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
@@ -10815,10 +10593,10 @@
       <c r="A78" s="2"/>
       <c r="B78" s="3"/>
       <c r="C78" s="2" t="s">
-        <v>560</v>
+        <v>523</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>561</v>
+        <v>524</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
@@ -10827,10 +10605,10 @@
       <c r="A79" s="2"/>
       <c r="B79" s="3"/>
       <c r="C79" s="2" t="s">
-        <v>562</v>
+        <v>525</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>563</v>
+        <v>526</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
@@ -10839,10 +10617,10 @@
       <c r="A80" s="2"/>
       <c r="B80" s="3"/>
       <c r="C80" s="2" t="s">
-        <v>564</v>
+        <v>527</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>565</v>
+        <v>528</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
@@ -10851,10 +10629,10 @@
       <c r="A81" s="2"/>
       <c r="B81" s="3"/>
       <c r="C81" s="2" t="s">
-        <v>566</v>
+        <v>529</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>567</v>
+        <v>530</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
@@ -10863,10 +10641,10 @@
       <c r="A82" s="2"/>
       <c r="B82" s="3"/>
       <c r="C82" s="2" t="s">
-        <v>568</v>
+        <v>531</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>569</v>
+        <v>532</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
@@ -10874,13 +10652,13 @@
     <row r="83" customHeight="1" spans="1:6">
       <c r="A83" s="2"/>
       <c r="B83" s="3" t="s">
-        <v>590</v>
+        <v>553</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>486</v>
+        <v>449</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>479</v>
+        <v>442</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>15</v>
@@ -10891,10 +10669,10 @@
       <c r="A84" s="2"/>
       <c r="B84" s="3"/>
       <c r="C84" s="2" t="s">
-        <v>454</v>
+        <v>417</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>455</v>
+        <v>418</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="2"/>
@@ -10903,10 +10681,10 @@
       <c r="A85" s="2"/>
       <c r="B85" s="3"/>
       <c r="C85" s="2" t="s">
-        <v>488</v>
+        <v>451</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>489</v>
+        <v>452</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
@@ -10915,10 +10693,10 @@
       <c r="A86" s="2"/>
       <c r="B86" s="3"/>
       <c r="C86" s="2" t="s">
-        <v>490</v>
+        <v>453</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>491</v>
+        <v>454</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
@@ -10927,10 +10705,10 @@
       <c r="A87" s="2"/>
       <c r="B87" s="3"/>
       <c r="C87" s="2" t="s">
-        <v>492</v>
+        <v>455</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>493</v>
+        <v>456</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2"/>
@@ -10939,10 +10717,10 @@
       <c r="A88" s="2"/>
       <c r="B88" s="3"/>
       <c r="C88" s="2" t="s">
-        <v>494</v>
+        <v>457</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" s="2"/>
@@ -10951,10 +10729,10 @@
       <c r="A89" s="2"/>
       <c r="B89" s="3"/>
       <c r="C89" s="2" t="s">
-        <v>496</v>
+        <v>459</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>497</v>
+        <v>460</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2"/>
@@ -10963,10 +10741,10 @@
       <c r="A90" s="2"/>
       <c r="B90" s="3"/>
       <c r="C90" s="2" t="s">
-        <v>498</v>
+        <v>461</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>499</v>
+        <v>462</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
@@ -10975,10 +10753,10 @@
       <c r="A91" s="2"/>
       <c r="B91" s="3"/>
       <c r="C91" s="2" t="s">
-        <v>500</v>
+        <v>463</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>501</v>
+        <v>464</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
@@ -10987,10 +10765,10 @@
       <c r="A92" s="2"/>
       <c r="B92" s="3"/>
       <c r="C92" s="2" t="s">
-        <v>502</v>
+        <v>465</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>503</v>
+        <v>466</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
@@ -10999,10 +10777,10 @@
       <c r="A93" s="2"/>
       <c r="B93" s="3"/>
       <c r="C93" s="2" t="s">
-        <v>504</v>
+        <v>467</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>505</v>
+        <v>468</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
@@ -11011,10 +10789,10 @@
       <c r="A94" s="2"/>
       <c r="B94" s="3"/>
       <c r="C94" s="2" t="s">
-        <v>506</v>
+        <v>469</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>507</v>
+        <v>470</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
@@ -11023,10 +10801,10 @@
       <c r="A95" s="2"/>
       <c r="B95" s="3"/>
       <c r="C95" s="2" t="s">
-        <v>508</v>
+        <v>471</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>509</v>
+        <v>472</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
@@ -11035,10 +10813,10 @@
       <c r="A96" s="2"/>
       <c r="B96" s="3"/>
       <c r="C96" s="2" t="s">
-        <v>510</v>
+        <v>473</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>511</v>
+        <v>474</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
@@ -11047,10 +10825,10 @@
       <c r="A97" s="2"/>
       <c r="B97" s="3"/>
       <c r="C97" s="2" t="s">
-        <v>560</v>
+        <v>523</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>561</v>
+        <v>524</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
@@ -11059,10 +10837,10 @@
       <c r="A98" s="2"/>
       <c r="B98" s="3"/>
       <c r="C98" s="2" t="s">
-        <v>562</v>
+        <v>525</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>563</v>
+        <v>526</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
@@ -11071,10 +10849,10 @@
       <c r="A99" s="2"/>
       <c r="B99" s="3"/>
       <c r="C99" s="2" t="s">
-        <v>564</v>
+        <v>527</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>565</v>
+        <v>528</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
@@ -11083,10 +10861,10 @@
       <c r="A100" s="2"/>
       <c r="B100" s="3"/>
       <c r="C100" s="2" t="s">
-        <v>566</v>
+        <v>529</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>567</v>
+        <v>530</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" s="2"/>
@@ -11095,10 +10873,10 @@
       <c r="A101" s="2"/>
       <c r="B101" s="3"/>
       <c r="C101" s="2" t="s">
-        <v>568</v>
+        <v>531</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>569</v>
+        <v>532</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
